--- a/data/compare.xlsx
+++ b/data/compare.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="GT_Byaz_220" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1829" uniqueCount="1424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1917" uniqueCount="1512">
   <si>
     <t>TG1VichyLightBlue220/33</t>
   </si>
@@ -4302,6 +4302,270 @@
   </si>
   <si>
     <t>TMoliva140150</t>
+  </si>
+  <si>
+    <t>TV-Tigers1-195x165</t>
+  </si>
+  <si>
+    <t>209521В</t>
+  </si>
+  <si>
+    <t>TV-Laguna1-195x165</t>
+  </si>
+  <si>
+    <t>197051В</t>
+  </si>
+  <si>
+    <t>TV-Cherepashki1-195x165</t>
+  </si>
+  <si>
+    <t>664671В</t>
+  </si>
+  <si>
+    <t>TV-Nektar1-195x165</t>
+  </si>
+  <si>
+    <t>662201В</t>
+  </si>
+  <si>
+    <t>TV-NejniyDen1-195x165</t>
+  </si>
+  <si>
+    <t>664641В</t>
+  </si>
+  <si>
+    <t>TV-LetnNoch1-195x165</t>
+  </si>
+  <si>
+    <t>664741В</t>
+  </si>
+  <si>
+    <t>TV-SpelieFrukti1-195x165</t>
+  </si>
+  <si>
+    <t>664711В</t>
+  </si>
+  <si>
+    <t>TV-Ailyn1-195x165</t>
+  </si>
+  <si>
+    <t>660221В</t>
+  </si>
+  <si>
+    <t>TV-Pletenie2-195x165</t>
+  </si>
+  <si>
+    <t>662852В</t>
+  </si>
+  <si>
+    <t>TV-NejnoeUtro1-195x165</t>
+  </si>
+  <si>
+    <t>664631В</t>
+  </si>
+  <si>
+    <t>TV-OvoshKorzin1-195x165</t>
+  </si>
+  <si>
+    <t>664951В</t>
+  </si>
+  <si>
+    <t>TV-KitayPeyzazh1-195x165</t>
+  </si>
+  <si>
+    <t>662231В</t>
+  </si>
+  <si>
+    <t>TV-Sebastyan1-195x165</t>
+  </si>
+  <si>
+    <t>TV-Ailyn2-195x165</t>
+  </si>
+  <si>
+    <t>660222В</t>
+  </si>
+  <si>
+    <t>TV-Asia1-195x165</t>
+  </si>
+  <si>
+    <t>661561В</t>
+  </si>
+  <si>
+    <t>TV-Kolyadki1-195x165</t>
+  </si>
+  <si>
+    <t>660541В</t>
+  </si>
+  <si>
+    <t>TV-Elochka1-195x165</t>
+  </si>
+  <si>
+    <t>662841В</t>
+  </si>
+  <si>
+    <t>TV-LimonKorzinka1-195x165</t>
+  </si>
+  <si>
+    <t>664091В</t>
+  </si>
+  <si>
+    <t>TV-Elis1-195x165</t>
+  </si>
+  <si>
+    <t>202431В</t>
+  </si>
+  <si>
+    <t>TV-EchoVesni1-195x165</t>
+  </si>
+  <si>
+    <t>665741В</t>
+  </si>
+  <si>
+    <t>TV-LetneeNastroen1-195x165</t>
+  </si>
+  <si>
+    <t>TV-Hutoryanka1-195x165</t>
+  </si>
+  <si>
+    <t>664081В</t>
+  </si>
+  <si>
+    <t>TV-VesenMelody1-195x165</t>
+  </si>
+  <si>
+    <t>665701В</t>
+  </si>
+  <si>
+    <t>TV-PodCvetomRozi1-195x165</t>
+  </si>
+  <si>
+    <t>664391В</t>
+  </si>
+  <si>
+    <t>TV-Lavanda1-195x165</t>
+  </si>
+  <si>
+    <t>197971В</t>
+  </si>
+  <si>
+    <t>TV-SlegkimParom1-195x165</t>
+  </si>
+  <si>
+    <t>195771В</t>
+  </si>
+  <si>
+    <t>TV-Mayolika1-195x165</t>
+  </si>
+  <si>
+    <t>664911В</t>
+  </si>
+  <si>
+    <t>TV-Tropicana1-195x165</t>
+  </si>
+  <si>
+    <t>208141В</t>
+  </si>
+  <si>
+    <t>TV-Kolyadki2-195x165</t>
+  </si>
+  <si>
+    <t>660542В</t>
+  </si>
+  <si>
+    <t>TV-LegkiyLepestok2-195x165</t>
+  </si>
+  <si>
+    <t>664372В</t>
+  </si>
+  <si>
+    <t>2046921819367</t>
+  </si>
+  <si>
+    <t>2046921819299</t>
+  </si>
+  <si>
+    <t>2046921819282</t>
+  </si>
+  <si>
+    <t>2046921819626</t>
+  </si>
+  <si>
+    <t>2046921819565</t>
+  </si>
+  <si>
+    <t>2046921819510</t>
+  </si>
+  <si>
+    <t>2046921819343</t>
+  </si>
+  <si>
+    <t>2046921819329</t>
+  </si>
+  <si>
+    <t>2046921819558</t>
+  </si>
+  <si>
+    <t>2046921819480</t>
+  </si>
+  <si>
+    <t>2046921819527</t>
+  </si>
+  <si>
+    <t>2046921819411</t>
+  </si>
+  <si>
+    <t>2046921819442</t>
+  </si>
+  <si>
+    <t>2046921819435</t>
+  </si>
+  <si>
+    <t>2046921819657</t>
+  </si>
+  <si>
+    <t>2046920701731</t>
+  </si>
+  <si>
+    <t>2046921819596</t>
+  </si>
+  <si>
+    <t>2046921819404</t>
+  </si>
+  <si>
+    <t>2046921819466</t>
+  </si>
+  <si>
+    <t>2046921671828</t>
+  </si>
+  <si>
+    <t>2046921819305</t>
+  </si>
+  <si>
+    <t>2046921819459</t>
+  </si>
+  <si>
+    <t>2046921819541</t>
+  </si>
+  <si>
+    <t>2046921819503</t>
+  </si>
+  <si>
+    <t>2046921819398</t>
+  </si>
+  <si>
+    <t>2046921819381</t>
+  </si>
+  <si>
+    <t>2046921819312</t>
+  </si>
+  <si>
+    <t>2046921819336</t>
+  </si>
+  <si>
+    <t>2046921819473</t>
+  </si>
+  <si>
+    <t>2046921819350</t>
   </si>
 </sst>
 </file>
@@ -4326,7 +4590,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -4345,16 +4609,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFC0C7CD"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9533,11 +9808,12 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C334"/>
+  <dimension ref="A1:C364"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="30.375" customWidth="1"/>
     <col min="2" max="2" width="14.375" customWidth="1"/>
+    <col min="3" max="3" width="19.875" style="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -9547,7 +9823,7 @@
       <c r="B1" t="s">
         <v>1040</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="6" t="s">
         <v>806</v>
       </c>
     </row>
@@ -9558,7 +9834,7 @@
       <c r="B2" t="s">
         <v>809</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="6" t="s">
         <v>805</v>
       </c>
     </row>
@@ -9569,7 +9845,7 @@
       <c r="B3" t="s">
         <v>810</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="6" t="s">
         <v>804</v>
       </c>
     </row>
@@ -9580,7 +9856,7 @@
       <c r="B4" t="s">
         <v>811</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="6" t="s">
         <v>803</v>
       </c>
     </row>
@@ -9591,7 +9867,7 @@
       <c r="B5" t="s">
         <v>812</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="6" t="s">
         <v>802</v>
       </c>
     </row>
@@ -9602,7 +9878,7 @@
       <c r="B6" t="s">
         <v>813</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="6" t="s">
         <v>801</v>
       </c>
     </row>
@@ -9613,7 +9889,7 @@
       <c r="B7" t="s">
         <v>814</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="6" t="s">
         <v>800</v>
       </c>
     </row>
@@ -9624,7 +9900,7 @@
       <c r="B8" t="s">
         <v>815</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="6" t="s">
         <v>799</v>
       </c>
     </row>
@@ -9635,7 +9911,7 @@
       <c r="B9" t="s">
         <v>816</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="6" t="s">
         <v>798</v>
       </c>
     </row>
@@ -9646,7 +9922,7 @@
       <c r="B10" t="s">
         <v>1041</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="6" t="s">
         <v>797</v>
       </c>
     </row>
@@ -9657,7 +9933,7 @@
       <c r="B11" t="s">
         <v>817</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="6" t="s">
         <v>796</v>
       </c>
     </row>
@@ -9668,7 +9944,7 @@
       <c r="B12" t="s">
         <v>818</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="6" t="s">
         <v>795</v>
       </c>
     </row>
@@ -9679,7 +9955,7 @@
       <c r="B13" t="s">
         <v>819</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="6" t="s">
         <v>794</v>
       </c>
     </row>
@@ -9690,7 +9966,7 @@
       <c r="B14" t="s">
         <v>807</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="6" t="s">
         <v>793</v>
       </c>
     </row>
@@ -9701,7 +9977,7 @@
       <c r="B15" t="s">
         <v>820</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="6" t="s">
         <v>792</v>
       </c>
     </row>
@@ -9712,7 +9988,7 @@
       <c r="B16" t="s">
         <v>821</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="6" t="s">
         <v>791</v>
       </c>
     </row>
@@ -9723,7 +9999,7 @@
       <c r="B17" t="s">
         <v>1042</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="6" t="s">
         <v>790</v>
       </c>
     </row>
@@ -9734,7 +10010,7 @@
       <c r="B18" t="s">
         <v>822</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="6" t="s">
         <v>789</v>
       </c>
     </row>
@@ -9745,7 +10021,7 @@
       <c r="B19" t="s">
         <v>823</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="6" t="s">
         <v>788</v>
       </c>
     </row>
@@ -9756,7 +10032,7 @@
       <c r="B20" t="s">
         <v>1038</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="6" t="s">
         <v>787</v>
       </c>
     </row>
@@ -9767,7 +10043,7 @@
       <c r="B21" t="s">
         <v>824</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="6" t="s">
         <v>786</v>
       </c>
     </row>
@@ -9778,7 +10054,7 @@
       <c r="B22" t="s">
         <v>825</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="6" t="s">
         <v>785</v>
       </c>
     </row>
@@ -9789,7 +10065,7 @@
       <c r="B23" t="s">
         <v>808</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="6" t="s">
         <v>784</v>
       </c>
     </row>
@@ -9800,7 +10076,7 @@
       <c r="B24" t="s">
         <v>826</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="6" t="s">
         <v>783</v>
       </c>
     </row>
@@ -9811,7 +10087,7 @@
       <c r="B25" t="s">
         <v>827</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="6" t="s">
         <v>782</v>
       </c>
     </row>
@@ -9822,7 +10098,7 @@
       <c r="B26" t="s">
         <v>828</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="6" t="s">
         <v>781</v>
       </c>
     </row>
@@ -9833,7 +10109,7 @@
       <c r="B27" t="s">
         <v>829</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="6" t="s">
         <v>780</v>
       </c>
     </row>
@@ -9844,7 +10120,7 @@
       <c r="B28" t="s">
         <v>830</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="6" t="s">
         <v>779</v>
       </c>
     </row>
@@ -9855,7 +10131,7 @@
       <c r="B29" t="s">
         <v>831</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="6" t="s">
         <v>778</v>
       </c>
     </row>
@@ -9866,7 +10142,7 @@
       <c r="B30" t="s">
         <v>832</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="6" t="s">
         <v>777</v>
       </c>
     </row>
@@ -9877,7 +10153,7 @@
       <c r="B31" t="s">
         <v>833</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="6" t="s">
         <v>776</v>
       </c>
     </row>
@@ -9888,7 +10164,7 @@
       <c r="B32" t="s">
         <v>834</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="6" t="s">
         <v>775</v>
       </c>
     </row>
@@ -9896,7 +10172,7 @@
       <c r="A33" t="s">
         <v>557</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="6" t="s">
         <v>774</v>
       </c>
     </row>
@@ -9907,7 +10183,7 @@
       <c r="B34" t="s">
         <v>835</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="6" t="s">
         <v>773</v>
       </c>
     </row>
@@ -9918,7 +10194,7 @@
       <c r="B35" t="s">
         <v>836</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="6" t="s">
         <v>772</v>
       </c>
     </row>
@@ -9929,7 +10205,7 @@
       <c r="B36" t="s">
         <v>1043</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="6" t="s">
         <v>771</v>
       </c>
     </row>
@@ -9940,7 +10216,7 @@
       <c r="B37" t="s">
         <v>837</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="6" t="s">
         <v>770</v>
       </c>
     </row>
@@ -9951,7 +10227,7 @@
       <c r="B38" t="s">
         <v>838</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="6" t="s">
         <v>769</v>
       </c>
     </row>
@@ -9962,7 +10238,7 @@
       <c r="B39" t="s">
         <v>1044</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="6" t="s">
         <v>768</v>
       </c>
     </row>
@@ -9973,7 +10249,7 @@
       <c r="B40" t="s">
         <v>1045</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="6" t="s">
         <v>767</v>
       </c>
     </row>
@@ -9984,7 +10260,7 @@
       <c r="B41" t="s">
         <v>1039</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="6" t="s">
         <v>766</v>
       </c>
     </row>
@@ -9995,7 +10271,7 @@
       <c r="B42" t="s">
         <v>839</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="6" t="s">
         <v>765</v>
       </c>
     </row>
@@ -10006,7 +10282,7 @@
       <c r="B43" t="s">
         <v>840</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="6" t="s">
         <v>764</v>
       </c>
     </row>
@@ -10017,7 +10293,7 @@
       <c r="B44" t="s">
         <v>841</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="6" t="s">
         <v>763</v>
       </c>
     </row>
@@ -10028,7 +10304,7 @@
       <c r="B45" t="s">
         <v>842</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="6" t="s">
         <v>762</v>
       </c>
     </row>
@@ -10039,7 +10315,7 @@
       <c r="B46" t="s">
         <v>1046</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="6" t="s">
         <v>761</v>
       </c>
     </row>
@@ -10050,7 +10326,7 @@
       <c r="B47" t="s">
         <v>843</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="6" t="s">
         <v>760</v>
       </c>
     </row>
@@ -10061,7 +10337,7 @@
       <c r="B48" t="s">
         <v>844</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="6" t="s">
         <v>759</v>
       </c>
     </row>
@@ -10072,7 +10348,7 @@
       <c r="B49" t="s">
         <v>845</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="6" t="s">
         <v>758</v>
       </c>
     </row>
@@ -10083,7 +10359,7 @@
       <c r="B50" t="s">
         <v>846</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="6" t="s">
         <v>757</v>
       </c>
     </row>
@@ -10094,7 +10370,7 @@
       <c r="B51" t="s">
         <v>847</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="6" t="s">
         <v>756</v>
       </c>
     </row>
@@ -10105,7 +10381,7 @@
       <c r="B52" t="s">
         <v>848</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="6" t="s">
         <v>755</v>
       </c>
     </row>
@@ -10116,7 +10392,7 @@
       <c r="B53" t="s">
         <v>849</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="6" t="s">
         <v>754</v>
       </c>
     </row>
@@ -10127,7 +10403,7 @@
       <c r="B54" t="s">
         <v>850</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" s="6" t="s">
         <v>753</v>
       </c>
     </row>
@@ -10138,7 +10414,7 @@
       <c r="B55" t="s">
         <v>851</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="6" t="s">
         <v>752</v>
       </c>
     </row>
@@ -10149,7 +10425,7 @@
       <c r="B56" t="s">
         <v>852</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" s="6" t="s">
         <v>751</v>
       </c>
     </row>
@@ -10160,7 +10436,7 @@
       <c r="B57" t="s">
         <v>853</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C57" s="6" t="s">
         <v>750</v>
       </c>
     </row>
@@ -10171,7 +10447,7 @@
       <c r="B58" t="s">
         <v>854</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="6" t="s">
         <v>749</v>
       </c>
     </row>
@@ -10182,7 +10458,7 @@
       <c r="B59" t="s">
         <v>855</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" s="6" t="s">
         <v>748</v>
       </c>
     </row>
@@ -10193,7 +10469,7 @@
       <c r="B60" t="s">
         <v>856</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="6" t="s">
         <v>747</v>
       </c>
     </row>
@@ -10204,7 +10480,7 @@
       <c r="B61" t="s">
         <v>857</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="6" t="s">
         <v>746</v>
       </c>
     </row>
@@ -10212,7 +10488,7 @@
       <c r="A62" t="s">
         <v>586</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="6" t="s">
         <v>745</v>
       </c>
     </row>
@@ -10220,7 +10496,7 @@
       <c r="A63" t="s">
         <v>587</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="6" t="s">
         <v>744</v>
       </c>
     </row>
@@ -10231,7 +10507,7 @@
       <c r="B64" t="s">
         <v>858</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" s="6" t="s">
         <v>743</v>
       </c>
     </row>
@@ -10242,7 +10518,7 @@
       <c r="B65" t="s">
         <v>859</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" s="6" t="s">
         <v>742</v>
       </c>
     </row>
@@ -10253,7 +10529,7 @@
       <c r="B66" t="s">
         <v>860</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C66" s="6" t="s">
         <v>741</v>
       </c>
     </row>
@@ -10264,7 +10540,7 @@
       <c r="B67" t="s">
         <v>861</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C67" s="6" t="s">
         <v>740</v>
       </c>
     </row>
@@ -10275,7 +10551,7 @@
       <c r="B68" t="s">
         <v>862</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C68" s="6" t="s">
         <v>739</v>
       </c>
     </row>
@@ -10283,7 +10559,7 @@
       <c r="A69" t="s">
         <v>593</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C69" s="6" t="s">
         <v>738</v>
       </c>
     </row>
@@ -10294,7 +10570,7 @@
       <c r="B70" t="s">
         <v>863</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C70" s="6" t="s">
         <v>737</v>
       </c>
     </row>
@@ -10305,7 +10581,7 @@
       <c r="B71" t="s">
         <v>864</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C71" s="6" t="s">
         <v>736</v>
       </c>
     </row>
@@ -10316,7 +10592,7 @@
       <c r="B72" t="s">
         <v>865</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C72" s="6" t="s">
         <v>735</v>
       </c>
     </row>
@@ -10327,7 +10603,7 @@
       <c r="B73" t="s">
         <v>866</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C73" s="6" t="s">
         <v>734</v>
       </c>
     </row>
@@ -10338,7 +10614,7 @@
       <c r="B74" t="s">
         <v>867</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C74" s="6" t="s">
         <v>733</v>
       </c>
     </row>
@@ -10349,7 +10625,7 @@
       <c r="B75" t="s">
         <v>868</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C75" s="6" t="s">
         <v>732</v>
       </c>
     </row>
@@ -10360,7 +10636,7 @@
       <c r="B76" t="s">
         <v>869</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C76" s="6" t="s">
         <v>731</v>
       </c>
     </row>
@@ -10368,7 +10644,7 @@
       <c r="A77" t="s">
         <v>601</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C77" s="6" t="s">
         <v>730</v>
       </c>
     </row>
@@ -10379,7 +10655,7 @@
       <c r="B78" t="s">
         <v>870</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C78" s="6" t="s">
         <v>729</v>
       </c>
     </row>
@@ -10390,7 +10666,7 @@
       <c r="B79" t="s">
         <v>871</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C79" s="6" t="s">
         <v>728</v>
       </c>
     </row>
@@ -10401,7 +10677,7 @@
       <c r="B80" t="s">
         <v>872</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C80" s="6" t="s">
         <v>727</v>
       </c>
     </row>
@@ -10412,7 +10688,7 @@
       <c r="B81" t="s">
         <v>873</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C81" s="6" t="s">
         <v>726</v>
       </c>
     </row>
@@ -10423,7 +10699,7 @@
       <c r="B82" t="s">
         <v>874</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C82" s="6" t="s">
         <v>725</v>
       </c>
     </row>
@@ -10434,7 +10710,7 @@
       <c r="B83" t="s">
         <v>875</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C83" s="6" t="s">
         <v>724</v>
       </c>
     </row>
@@ -10445,7 +10721,7 @@
       <c r="B84" t="s">
         <v>876</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C84" s="6" t="s">
         <v>723</v>
       </c>
     </row>
@@ -10456,7 +10732,7 @@
       <c r="B85" t="s">
         <v>877</v>
       </c>
-      <c r="C85" t="s">
+      <c r="C85" s="6" t="s">
         <v>722</v>
       </c>
     </row>
@@ -10467,7 +10743,7 @@
       <c r="B86" t="s">
         <v>878</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C86" s="6" t="s">
         <v>721</v>
       </c>
     </row>
@@ -10478,7 +10754,7 @@
       <c r="B87" t="s">
         <v>879</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C87" s="6" t="s">
         <v>720</v>
       </c>
     </row>
@@ -10489,7 +10765,7 @@
       <c r="B88" t="s">
         <v>880</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C88" s="6" t="s">
         <v>719</v>
       </c>
     </row>
@@ -10500,7 +10776,7 @@
       <c r="B89" t="s">
         <v>881</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C89" s="6" t="s">
         <v>718</v>
       </c>
     </row>
@@ -10511,7 +10787,7 @@
       <c r="B90" t="s">
         <v>882</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C90" s="6" t="s">
         <v>717</v>
       </c>
     </row>
@@ -10522,7 +10798,7 @@
       <c r="B91" t="s">
         <v>883</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C91" s="6" t="s">
         <v>716</v>
       </c>
     </row>
@@ -10533,7 +10809,7 @@
       <c r="B92" t="s">
         <v>884</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C92" s="6" t="s">
         <v>715</v>
       </c>
     </row>
@@ -10544,7 +10820,7 @@
       <c r="B93" t="s">
         <v>885</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C93" s="6" t="s">
         <v>714</v>
       </c>
     </row>
@@ -10555,7 +10831,7 @@
       <c r="B94" t="s">
         <v>886</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C94" s="6" t="s">
         <v>713</v>
       </c>
     </row>
@@ -10566,7 +10842,7 @@
       <c r="B95" t="s">
         <v>887</v>
       </c>
-      <c r="C95" t="s">
+      <c r="C95" s="6" t="s">
         <v>712</v>
       </c>
     </row>
@@ -10577,7 +10853,7 @@
       <c r="B96" t="s">
         <v>888</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C96" s="6" t="s">
         <v>711</v>
       </c>
     </row>
@@ -10588,7 +10864,7 @@
       <c r="B97" t="s">
         <v>889</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C97" s="6" t="s">
         <v>710</v>
       </c>
     </row>
@@ -10599,7 +10875,7 @@
       <c r="B98" t="s">
         <v>890</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C98" s="6" t="s">
         <v>709</v>
       </c>
     </row>
@@ -10610,7 +10886,7 @@
       <c r="B99" t="s">
         <v>891</v>
       </c>
-      <c r="C99" t="s">
+      <c r="C99" s="6" t="s">
         <v>708</v>
       </c>
     </row>
@@ -10621,7 +10897,7 @@
       <c r="B100" t="s">
         <v>892</v>
       </c>
-      <c r="C100" t="s">
+      <c r="C100" s="6" t="s">
         <v>707</v>
       </c>
     </row>
@@ -10632,7 +10908,7 @@
       <c r="B101" t="s">
         <v>893</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C101" s="6" t="s">
         <v>706</v>
       </c>
     </row>
@@ -10643,7 +10919,7 @@
       <c r="B102" t="s">
         <v>894</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C102" s="6" t="s">
         <v>705</v>
       </c>
     </row>
@@ -10654,7 +10930,7 @@
       <c r="B103" t="s">
         <v>895</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C103" s="6" t="s">
         <v>704</v>
       </c>
     </row>
@@ -10665,7 +10941,7 @@
       <c r="B104" t="s">
         <v>896</v>
       </c>
-      <c r="C104" t="s">
+      <c r="C104" s="6" t="s">
         <v>703</v>
       </c>
     </row>
@@ -10676,7 +10952,7 @@
       <c r="B105" t="s">
         <v>897</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C105" s="6" t="s">
         <v>702</v>
       </c>
     </row>
@@ -10687,7 +10963,7 @@
       <c r="B106" t="s">
         <v>898</v>
       </c>
-      <c r="C106" t="s">
+      <c r="C106" s="6" t="s">
         <v>701</v>
       </c>
     </row>
@@ -10698,7 +10974,7 @@
       <c r="B107" t="s">
         <v>899</v>
       </c>
-      <c r="C107" t="s">
+      <c r="C107" s="6" t="s">
         <v>700</v>
       </c>
     </row>
@@ -10709,7 +10985,7 @@
       <c r="B108" t="s">
         <v>900</v>
       </c>
-      <c r="C108" t="s">
+      <c r="C108" s="6" t="s">
         <v>699</v>
       </c>
     </row>
@@ -10720,7 +10996,7 @@
       <c r="B109" t="s">
         <v>901</v>
       </c>
-      <c r="C109" t="s">
+      <c r="C109" s="6" t="s">
         <v>698</v>
       </c>
     </row>
@@ -10731,7 +11007,7 @@
       <c r="B110" t="s">
         <v>902</v>
       </c>
-      <c r="C110" t="s">
+      <c r="C110" s="6" t="s">
         <v>697</v>
       </c>
     </row>
@@ -10742,7 +11018,7 @@
       <c r="B111" t="s">
         <v>903</v>
       </c>
-      <c r="C111" t="s">
+      <c r="C111" s="6" t="s">
         <v>696</v>
       </c>
     </row>
@@ -10753,7 +11029,7 @@
       <c r="B112" t="s">
         <v>904</v>
       </c>
-      <c r="C112" t="s">
+      <c r="C112" s="6" t="s">
         <v>695</v>
       </c>
     </row>
@@ -10764,7 +11040,7 @@
       <c r="B113" t="s">
         <v>905</v>
       </c>
-      <c r="C113" t="s">
+      <c r="C113" s="6" t="s">
         <v>694</v>
       </c>
     </row>
@@ -10775,7 +11051,7 @@
       <c r="B114" t="s">
         <v>906</v>
       </c>
-      <c r="C114" t="s">
+      <c r="C114" s="6" t="s">
         <v>693</v>
       </c>
     </row>
@@ -10786,7 +11062,7 @@
       <c r="B115" t="s">
         <v>907</v>
       </c>
-      <c r="C115" t="s">
+      <c r="C115" s="6" t="s">
         <v>692</v>
       </c>
     </row>
@@ -10797,7 +11073,7 @@
       <c r="B116" t="s">
         <v>908</v>
       </c>
-      <c r="C116" t="s">
+      <c r="C116" s="6" t="s">
         <v>691</v>
       </c>
     </row>
@@ -10808,7 +11084,7 @@
       <c r="B117" t="s">
         <v>909</v>
       </c>
-      <c r="C117" t="s">
+      <c r="C117" s="6" t="s">
         <v>690</v>
       </c>
     </row>
@@ -10819,7 +11095,7 @@
       <c r="B118" t="s">
         <v>910</v>
       </c>
-      <c r="C118" t="s">
+      <c r="C118" s="6" t="s">
         <v>689</v>
       </c>
     </row>
@@ -10830,7 +11106,7 @@
       <c r="B119" t="s">
         <v>911</v>
       </c>
-      <c r="C119" t="s">
+      <c r="C119" s="6" t="s">
         <v>688</v>
       </c>
     </row>
@@ -10841,7 +11117,7 @@
       <c r="B120" t="s">
         <v>912</v>
       </c>
-      <c r="C120" t="s">
+      <c r="C120" s="6" t="s">
         <v>687</v>
       </c>
     </row>
@@ -10852,7 +11128,7 @@
       <c r="B121" t="s">
         <v>913</v>
       </c>
-      <c r="C121" t="s">
+      <c r="C121" s="6" t="s">
         <v>686</v>
       </c>
     </row>
@@ -10863,7 +11139,7 @@
       <c r="B122" t="s">
         <v>914</v>
       </c>
-      <c r="C122" t="s">
+      <c r="C122" s="6" t="s">
         <v>685</v>
       </c>
     </row>
@@ -10874,7 +11150,7 @@
       <c r="B123" t="s">
         <v>915</v>
       </c>
-      <c r="C123" t="s">
+      <c r="C123" s="6" t="s">
         <v>684</v>
       </c>
     </row>
@@ -10885,7 +11161,7 @@
       <c r="B124" t="s">
         <v>916</v>
       </c>
-      <c r="C124" t="s">
+      <c r="C124" s="6" t="s">
         <v>683</v>
       </c>
     </row>
@@ -10896,7 +11172,7 @@
       <c r="B125" t="s">
         <v>917</v>
       </c>
-      <c r="C125" t="s">
+      <c r="C125" s="6" t="s">
         <v>682</v>
       </c>
     </row>
@@ -10907,7 +11183,7 @@
       <c r="B126" t="s">
         <v>918</v>
       </c>
-      <c r="C126" t="s">
+      <c r="C126" s="6" t="s">
         <v>681</v>
       </c>
     </row>
@@ -10918,7 +11194,7 @@
       <c r="B127" t="s">
         <v>919</v>
       </c>
-      <c r="C127" t="s">
+      <c r="C127" s="6" t="s">
         <v>680</v>
       </c>
     </row>
@@ -10929,7 +11205,7 @@
       <c r="B128" t="s">
         <v>920</v>
       </c>
-      <c r="C128" t="s">
+      <c r="C128" s="6" t="s">
         <v>679</v>
       </c>
     </row>
@@ -10940,7 +11216,7 @@
       <c r="B129" t="s">
         <v>921</v>
       </c>
-      <c r="C129" t="s">
+      <c r="C129" s="6" t="s">
         <v>678</v>
       </c>
     </row>
@@ -10951,7 +11227,7 @@
       <c r="B130" t="s">
         <v>922</v>
       </c>
-      <c r="C130" t="s">
+      <c r="C130" s="6" t="s">
         <v>677</v>
       </c>
     </row>
@@ -10962,7 +11238,7 @@
       <c r="B131" t="s">
         <v>923</v>
       </c>
-      <c r="C131" t="s">
+      <c r="C131" s="6" t="s">
         <v>676</v>
       </c>
     </row>
@@ -10973,7 +11249,7 @@
       <c r="B132" t="s">
         <v>924</v>
       </c>
-      <c r="C132" t="s">
+      <c r="C132" s="6" t="s">
         <v>675</v>
       </c>
     </row>
@@ -10984,7 +11260,7 @@
       <c r="B133" t="s">
         <v>925</v>
       </c>
-      <c r="C133" t="s">
+      <c r="C133" s="6" t="s">
         <v>674</v>
       </c>
     </row>
@@ -10995,7 +11271,7 @@
       <c r="B134" t="s">
         <v>926</v>
       </c>
-      <c r="C134" t="s">
+      <c r="C134" s="6" t="s">
         <v>673</v>
       </c>
     </row>
@@ -11006,7 +11282,7 @@
       <c r="B135" t="s">
         <v>927</v>
       </c>
-      <c r="C135" t="s">
+      <c r="C135" s="6" t="s">
         <v>672</v>
       </c>
     </row>
@@ -11017,7 +11293,7 @@
       <c r="B136" t="s">
         <v>928</v>
       </c>
-      <c r="C136" t="s">
+      <c r="C136" s="6" t="s">
         <v>671</v>
       </c>
     </row>
@@ -11028,7 +11304,7 @@
       <c r="B137" t="s">
         <v>929</v>
       </c>
-      <c r="C137" t="s">
+      <c r="C137" s="6" t="s">
         <v>670</v>
       </c>
     </row>
@@ -11039,7 +11315,7 @@
       <c r="B138" t="s">
         <v>930</v>
       </c>
-      <c r="C138" t="s">
+      <c r="C138" s="6" t="s">
         <v>669</v>
       </c>
     </row>
@@ -11050,7 +11326,7 @@
       <c r="B139" t="s">
         <v>931</v>
       </c>
-      <c r="C139" t="s">
+      <c r="C139" s="6" t="s">
         <v>668</v>
       </c>
     </row>
@@ -11061,7 +11337,7 @@
       <c r="B140" t="s">
         <v>932</v>
       </c>
-      <c r="C140" t="s">
+      <c r="C140" s="6" t="s">
         <v>667</v>
       </c>
     </row>
@@ -11072,7 +11348,7 @@
       <c r="B141" t="s">
         <v>933</v>
       </c>
-      <c r="C141" t="s">
+      <c r="C141" s="6" t="s">
         <v>666</v>
       </c>
     </row>
@@ -12496,7 +12772,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="321" spans="1:2">
+    <row r="321" spans="1:3">
       <c r="A321" s="1" t="s">
         <v>1276</v>
       </c>
@@ -12504,7 +12780,7 @@
         <v>1345</v>
       </c>
     </row>
-    <row r="322" spans="1:2">
+    <row r="322" spans="1:3">
       <c r="A322" s="1" t="s">
         <v>1277</v>
       </c>
@@ -12512,7 +12788,7 @@
         <v>1346</v>
       </c>
     </row>
-    <row r="323" spans="1:2">
+    <row r="323" spans="1:3">
       <c r="A323" s="1" t="s">
         <v>1278</v>
       </c>
@@ -12520,7 +12796,7 @@
         <v>1347</v>
       </c>
     </row>
-    <row r="324" spans="1:2">
+    <row r="324" spans="1:3">
       <c r="A324" s="1" t="s">
         <v>1279</v>
       </c>
@@ -12528,7 +12804,7 @@
         <v>1348</v>
       </c>
     </row>
-    <row r="325" spans="1:2">
+    <row r="325" spans="1:3">
       <c r="A325" s="1" t="s">
         <v>1280</v>
       </c>
@@ -12536,7 +12812,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="326" spans="1:2">
+    <row r="326" spans="1:3">
       <c r="A326" s="1" t="s">
         <v>1281</v>
       </c>
@@ -12544,7 +12820,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="327" spans="1:2">
+    <row r="327" spans="1:3">
       <c r="A327" s="1" t="s">
         <v>1282</v>
       </c>
@@ -12552,7 +12828,7 @@
         <v>1351</v>
       </c>
     </row>
-    <row r="328" spans="1:2">
+    <row r="328" spans="1:3">
       <c r="A328" s="1" t="s">
         <v>1283</v>
       </c>
@@ -12560,7 +12836,7 @@
         <v>1352</v>
       </c>
     </row>
-    <row r="329" spans="1:2">
+    <row r="329" spans="1:3">
       <c r="A329" s="1" t="s">
         <v>1284</v>
       </c>
@@ -12568,7 +12844,7 @@
         <v>1353</v>
       </c>
     </row>
-    <row r="330" spans="1:2">
+    <row r="330" spans="1:3">
       <c r="A330" s="1" t="s">
         <v>1285</v>
       </c>
@@ -12576,7 +12852,7 @@
         <v>1354</v>
       </c>
     </row>
-    <row r="331" spans="1:2">
+    <row r="331" spans="1:3">
       <c r="A331" s="1" t="s">
         <v>1286</v>
       </c>
@@ -12584,7 +12860,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="332" spans="1:2">
+    <row r="332" spans="1:3">
       <c r="A332" s="1" t="s">
         <v>1287</v>
       </c>
@@ -12592,7 +12868,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="333" spans="1:2">
+    <row r="333" spans="1:3">
       <c r="A333" s="1" t="s">
         <v>1288</v>
       </c>
@@ -12600,9 +12876,333 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="334" spans="1:2">
+    <row r="334" spans="1:3">
       <c r="A334" s="1" t="s">
         <v>1289</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3">
+      <c r="A335" s="5" t="s">
+        <v>1424</v>
+      </c>
+      <c r="B335" t="s">
+        <v>1425</v>
+      </c>
+      <c r="C335" s="6" t="s">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3">
+      <c r="A336" s="5" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B336" t="s">
+        <v>1427</v>
+      </c>
+      <c r="C336" s="6" t="s">
+        <v>1483</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3">
+      <c r="A337" s="5" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B337" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C337" s="6" t="s">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3">
+      <c r="A338" s="5" t="s">
+        <v>1430</v>
+      </c>
+      <c r="B338" t="s">
+        <v>1431</v>
+      </c>
+      <c r="C338" s="6" t="s">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3">
+      <c r="A339" s="5" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B339" t="s">
+        <v>1433</v>
+      </c>
+      <c r="C339" s="6" t="s">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3">
+      <c r="A340" s="5" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B340" t="s">
+        <v>1435</v>
+      </c>
+      <c r="C340" s="6" t="s">
+        <v>1487</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3">
+      <c r="A341" s="5" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B341" t="s">
+        <v>1437</v>
+      </c>
+      <c r="C341" s="6" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3">
+      <c r="A342" s="5" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B342" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C342" s="6" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3">
+      <c r="A343" s="5" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B343" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C343" s="6" t="s">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3">
+      <c r="A344" s="5" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B344" t="s">
+        <v>1443</v>
+      </c>
+      <c r="C344" s="6" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3">
+      <c r="A345" s="5" t="s">
+        <v>1444</v>
+      </c>
+      <c r="B345" t="s">
+        <v>1445</v>
+      </c>
+      <c r="C345" s="6" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3">
+      <c r="A346" s="5" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B346" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C346" s="6" t="s">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3">
+      <c r="A347" s="5" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C347" s="6" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3">
+      <c r="A348" s="5" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B348" t="s">
+        <v>1450</v>
+      </c>
+      <c r="C348" s="6" t="s">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3">
+      <c r="A349" s="5" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B349" t="s">
+        <v>1452</v>
+      </c>
+      <c r="C349" s="6" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3">
+      <c r="A350" s="5" t="s">
+        <v>1453</v>
+      </c>
+      <c r="B350" t="s">
+        <v>1454</v>
+      </c>
+      <c r="C350" s="6" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3">
+      <c r="A351" s="5" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B351" t="s">
+        <v>1456</v>
+      </c>
+      <c r="C351" s="6" t="s">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3">
+      <c r="A352" s="5" t="s">
+        <v>1457</v>
+      </c>
+      <c r="B352" t="s">
+        <v>1458</v>
+      </c>
+      <c r="C352" s="6" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3">
+      <c r="A353" s="5" t="s">
+        <v>1459</v>
+      </c>
+      <c r="B353" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C353" s="6" t="s">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3">
+      <c r="A354" s="5" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B354" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C354" s="6" t="s">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3">
+      <c r="A355" s="5" t="s">
+        <v>1463</v>
+      </c>
+      <c r="C355" s="6" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3">
+      <c r="A356" s="5" t="s">
+        <v>1464</v>
+      </c>
+      <c r="B356" t="s">
+        <v>1465</v>
+      </c>
+      <c r="C356" s="6" t="s">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3">
+      <c r="A357" s="5" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B357" t="s">
+        <v>1467</v>
+      </c>
+      <c r="C357" s="6" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3">
+      <c r="A358" s="5" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B358" t="s">
+        <v>1469</v>
+      </c>
+      <c r="C358" s="6" t="s">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3">
+      <c r="A359" s="5" t="s">
+        <v>1470</v>
+      </c>
+      <c r="B359" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C359" s="6" t="s">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3">
+      <c r="A360" s="5" t="s">
+        <v>1472</v>
+      </c>
+      <c r="B360" t="s">
+        <v>1473</v>
+      </c>
+      <c r="C360" s="6" t="s">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3">
+      <c r="A361" s="5" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B361" t="s">
+        <v>1475</v>
+      </c>
+      <c r="C361" s="6" t="s">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3">
+      <c r="A362" s="5" t="s">
+        <v>1476</v>
+      </c>
+      <c r="B362" t="s">
+        <v>1477</v>
+      </c>
+      <c r="C362" s="6" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3">
+      <c r="A363" s="5" t="s">
+        <v>1478</v>
+      </c>
+      <c r="B363" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C363" s="6" t="s">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3">
+      <c r="A364" s="5" t="s">
+        <v>1480</v>
+      </c>
+      <c r="B364" t="s">
+        <v>1481</v>
+      </c>
+      <c r="C364" s="6" t="s">
+        <v>1510</v>
       </c>
     </row>
   </sheetData>

--- a/data/compare.xlsx
+++ b/data/compare.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="GT_Byaz_220" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="GT_Byaz_150_140_Solid" sheetId="7" r:id="rId5"/>
     <sheet name="GT_Poplin_220" sheetId="3" r:id="rId6"/>
     <sheet name="TD" sheetId="4" r:id="rId7"/>
+    <sheet name="AD" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="162913" refMode="R1C1"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1917" uniqueCount="1512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2372" uniqueCount="1966">
   <si>
     <t>TG1VichyLightBlue220/33</t>
   </si>
@@ -4566,6 +4567,1368 @@
   </si>
   <si>
     <t>2046921819350</t>
+  </si>
+  <si>
+    <t>AD-220120-VishiOSN-8</t>
+  </si>
+  <si>
+    <t>Виши Бязь набивная 220см рис. 12709-1</t>
+  </si>
+  <si>
+    <t>Я018435</t>
+  </si>
+  <si>
+    <t>AD-220120-DomUyutOSN-8</t>
+  </si>
+  <si>
+    <t>Домашний уют Бязь набив. 220 см рис.11789-1</t>
+  </si>
+  <si>
+    <t>Я010820</t>
+  </si>
+  <si>
+    <t>AD-220120-UltramarinOSN-8</t>
+  </si>
+  <si>
+    <t>Ультрамарин Бязь набивная 220см рис. 13210-1</t>
+  </si>
+  <si>
+    <t>Я024645</t>
+  </si>
+  <si>
+    <t>AD-220120-KapigusiOSN-8</t>
+  </si>
+  <si>
+    <t>Капигуси Бязь набивная 220см рис. 13449-1</t>
+  </si>
+  <si>
+    <t>Я028129</t>
+  </si>
+  <si>
+    <t>AD-220120-KotovasiyaKOMP-8</t>
+  </si>
+  <si>
+    <t>Котовасия Комп.Бязь набивная 220см рис. 13050-1</t>
+  </si>
+  <si>
+    <t>Я021522</t>
+  </si>
+  <si>
+    <t>AD-220120-DenimKOMP-8</t>
+  </si>
+  <si>
+    <t>Деним Комп.Бязь набивная 220см рис. 13065-1</t>
+  </si>
+  <si>
+    <t>Я021619</t>
+  </si>
+  <si>
+    <t>AD-220120-StraykKOMP-8</t>
+  </si>
+  <si>
+    <t>Страйк Комп.Бязь набивная 220см рис. 12971-1</t>
+  </si>
+  <si>
+    <t>Я020440</t>
+  </si>
+  <si>
+    <t>AD-220120-DenimOSN-8</t>
+  </si>
+  <si>
+    <t>Деним Бязь набивная 220см рис. 13064-1</t>
+  </si>
+  <si>
+    <t>Я021618</t>
+  </si>
+  <si>
+    <t>AD-220120-SenorKOMP-8</t>
+  </si>
+  <si>
+    <t>Сеньор Комп.Бязь набив. 220 см рис.12316-1</t>
+  </si>
+  <si>
+    <t>Я015090</t>
+  </si>
+  <si>
+    <t>AD-220120-DomUyutKOMP-8</t>
+  </si>
+  <si>
+    <t>Домашний уют Комп. бязь набив. 220 см рис.11790-1</t>
+  </si>
+  <si>
+    <t>Я010821</t>
+  </si>
+  <si>
+    <t>AD-220120-IntonatsiyaKOMP-8</t>
+  </si>
+  <si>
+    <t>Интонация Комп.Бязь набив. 220 см рис.11707-1</t>
+  </si>
+  <si>
+    <t>Я010191</t>
+  </si>
+  <si>
+    <t>AD-220120-RomansOSN-8</t>
+  </si>
+  <si>
+    <t>Романс Бязь набивная 220см рис. 12830-1</t>
+  </si>
+  <si>
+    <t>Я019945</t>
+  </si>
+  <si>
+    <t>AD-220120-ShyelkOSN-8</t>
+  </si>
+  <si>
+    <t>Шёлк Бязь набивная 220см рис. 13157-1</t>
+  </si>
+  <si>
+    <t>Я024413</t>
+  </si>
+  <si>
+    <t>AD-220120-AlbertOSN-8</t>
+  </si>
+  <si>
+    <t>Альберт.Бязь набив. 220 см рис.12867-1</t>
+  </si>
+  <si>
+    <t>Я019906</t>
+  </si>
+  <si>
+    <t>AD-220120-BenefisKOMP-8</t>
+  </si>
+  <si>
+    <t>Бенефис Комп.Бязь набив. 220 см рис.11607-1</t>
+  </si>
+  <si>
+    <t>Я009174</t>
+  </si>
+  <si>
+    <t>AD-220120-GarmoniyaOSN-8</t>
+  </si>
+  <si>
+    <t>Гармония Бязь набивная 220см рис. 13130-1</t>
+  </si>
+  <si>
+    <t>Я022878</t>
+  </si>
+  <si>
+    <t>AD-220120-IridaOSN-8</t>
+  </si>
+  <si>
+    <t>Ирида Бязь набивная 220см рис. 13051-1</t>
+  </si>
+  <si>
+    <t>Я023883</t>
+  </si>
+  <si>
+    <t>AD-220120-VishneviySadOSN-8</t>
+  </si>
+  <si>
+    <t>Вишневый сад Бязь набивная 220см рис. 13082-1</t>
+  </si>
+  <si>
+    <t>Я022012</t>
+  </si>
+  <si>
+    <t>AD-220120-EffektOSN-8</t>
+  </si>
+  <si>
+    <t>Эффект Бязь набивная 220см рис. 13335-1</t>
+  </si>
+  <si>
+    <t>Я026576</t>
+  </si>
+  <si>
+    <t>AD-220120-BelkantoKOMP-8</t>
+  </si>
+  <si>
+    <t>Бельканто Комп.Бязь набивная 220см рис. 13135-1</t>
+  </si>
+  <si>
+    <t>Я022936</t>
+  </si>
+  <si>
+    <t>AD-220120-ElbrusKOMP-8</t>
+  </si>
+  <si>
+    <t>Эльбрус Комп.Бязь набив. 220 см рис.11888-1</t>
+  </si>
+  <si>
+    <t>Я011450</t>
+  </si>
+  <si>
+    <t>AD-220120-MagnoliyaKOMP-8</t>
+  </si>
+  <si>
+    <t>Магнолия Комп. Бязь набив. 220 см рис.13274-1</t>
+  </si>
+  <si>
+    <t>Я025106</t>
+  </si>
+  <si>
+    <t>AD-220120-BenefisOSN-8</t>
+  </si>
+  <si>
+    <t>Бенефис Бязь набив. 220 см рис.11606-1</t>
+  </si>
+  <si>
+    <t>Я009173</t>
+  </si>
+  <si>
+    <t>AD-220120-RodosKOMP-8</t>
+  </si>
+  <si>
+    <t>Родос Комп.Бязь набивная 220см рис. 13046-1</t>
+  </si>
+  <si>
+    <t>Я021871</t>
+  </si>
+  <si>
+    <t>AD-220120-StraykOSN-8</t>
+  </si>
+  <si>
+    <t>Страйк Бязь набивная 220см рис. 12970-1</t>
+  </si>
+  <si>
+    <t>Я020439</t>
+  </si>
+  <si>
+    <t>AD-220120-MurritoKOMP-8</t>
+  </si>
+  <si>
+    <t>Муррито Комп. Бязь набив. 220 см рис.13289-1</t>
+  </si>
+  <si>
+    <t>Я026184</t>
+  </si>
+  <si>
+    <t>AD-220120-KameoOSN-8</t>
+  </si>
+  <si>
+    <t>Камео Бязь набивная 220см рис. 13111-1</t>
+  </si>
+  <si>
+    <t>Я022632</t>
+  </si>
+  <si>
+    <t>AD-220120-AzaliyaKOMP-8</t>
+  </si>
+  <si>
+    <t>Азалия Комп. Бязь набив. 220 см рис.23163-1</t>
+  </si>
+  <si>
+    <t>Я021453</t>
+  </si>
+  <si>
+    <t>AD-220120-SmaylOSN-8</t>
+  </si>
+  <si>
+    <t>Смайл Бязь набивная 220см рис. 13357-1</t>
+  </si>
+  <si>
+    <t>Я026913</t>
+  </si>
+  <si>
+    <t>AD-220120-ModistkaOSN-8</t>
+  </si>
+  <si>
+    <t>Модистка Бязь набивная 220см рис. 13340-1</t>
+  </si>
+  <si>
+    <t>Я026806</t>
+  </si>
+  <si>
+    <t>AD-220120-Korsika-8</t>
+  </si>
+  <si>
+    <t>Корсика Комп.Бязь набив. 220 см рис. 12562-1</t>
+  </si>
+  <si>
+    <t>Я017535</t>
+  </si>
+  <si>
+    <t>AD-220120-ShikOSN-8</t>
+  </si>
+  <si>
+    <t>Шик Бязь набив. 220 см рис.12398-1</t>
+  </si>
+  <si>
+    <t>Я014921</t>
+  </si>
+  <si>
+    <t>AD-220120-TerriKOMP-8</t>
+  </si>
+  <si>
+    <t>Терри Комп.Бязь набивная 220см рис. 13424-2</t>
+  </si>
+  <si>
+    <t>Я027976</t>
+  </si>
+  <si>
+    <t>AD-220120-Enigma-8</t>
+  </si>
+  <si>
+    <t>Энигма Бязь набив. 220 см рис.12492-1</t>
+  </si>
+  <si>
+    <t>Я016238</t>
+  </si>
+  <si>
+    <t>AD-220120-TsvetokZhelaniyKOMP-8</t>
+  </si>
+  <si>
+    <t>Цветок желаний Компаньон.Бязь набив. 220 см рис.12321-1</t>
+  </si>
+  <si>
+    <t>Я015037</t>
+  </si>
+  <si>
+    <t>AD-220120-SherriOSN-8</t>
+  </si>
+  <si>
+    <t>Шерри Бязь набивная 220см рис. 13363-1</t>
+  </si>
+  <si>
+    <t>Я027241</t>
+  </si>
+  <si>
+    <t>AD-220120-SaraOSN-8</t>
+  </si>
+  <si>
+    <t>Сара Бязь набив. 220 см рис.13252-1</t>
+  </si>
+  <si>
+    <t>Я024825</t>
+  </si>
+  <si>
+    <t>AD-220120-YasminaOSN-8</t>
+  </si>
+  <si>
+    <t>Ясмина Бязь набивная 220см рис. 13275-1</t>
+  </si>
+  <si>
+    <t>Я025104</t>
+  </si>
+  <si>
+    <t>AD-220120-ZhenevaOSN-8</t>
+  </si>
+  <si>
+    <t>Женева Бязь набив. 220 см рис.11140-1</t>
+  </si>
+  <si>
+    <t>Я003472</t>
+  </si>
+  <si>
+    <t>AD-220120-KameoKOMP-8</t>
+  </si>
+  <si>
+    <t>Камео Комп.Бязь набивная 220см рис. 13112-1</t>
+  </si>
+  <si>
+    <t>Я022633</t>
+  </si>
+  <si>
+    <t>AD-220120-Glamur-8</t>
+  </si>
+  <si>
+    <t>Гламур Комп.Бязь набив. 220 см рис.11609-1</t>
+  </si>
+  <si>
+    <t>Я009289</t>
+  </si>
+  <si>
+    <t>AD-220120-SevernayaKoronaOSN-8</t>
+  </si>
+  <si>
+    <t>Северная корона Бязь набивная 220см рис. 13042-1</t>
+  </si>
+  <si>
+    <t>Я024643</t>
+  </si>
+  <si>
+    <t>AD-220120-AntuanettaOSN-8</t>
+  </si>
+  <si>
+    <t>Антуанетта Бязь набивная 220см рис. 13306-1</t>
+  </si>
+  <si>
+    <t>Я026264</t>
+  </si>
+  <si>
+    <t>AD-220120-SerebryanList-8</t>
+  </si>
+  <si>
+    <t>Серебряные листья Ком.Бязь набивная 220см рис. 12692-1</t>
+  </si>
+  <si>
+    <t>Я018332</t>
+  </si>
+  <si>
+    <t>AD-220120-IridaKOMP-8</t>
+  </si>
+  <si>
+    <t>Ирида Комп.Бязь набивная 220см рис. 13052-1</t>
+  </si>
+  <si>
+    <t>Я023884</t>
+  </si>
+  <si>
+    <t>AD-220120-MayronOSN-8</t>
+  </si>
+  <si>
+    <t>Майрон Бязь набивная 220см рис. 13022-1</t>
+  </si>
+  <si>
+    <t>Я021092</t>
+  </si>
+  <si>
+    <t>AD-220120-ValsKOMP-8</t>
+  </si>
+  <si>
+    <t>Вальс Комп. Бязь набив. 220 см рис.12613-1</t>
+  </si>
+  <si>
+    <t>Я018016</t>
+  </si>
+  <si>
+    <t>AD-220120-NevesomostOSN-8</t>
+  </si>
+  <si>
+    <t>Невесомость Бязь набивная 220см рис. 12941-1</t>
+  </si>
+  <si>
+    <t>Я020879</t>
+  </si>
+  <si>
+    <t>AD-220120-dzhoystikKOMP-8</t>
+  </si>
+  <si>
+    <t>Джойстик Комп.Бязь набивная 220см рис. 13419-1</t>
+  </si>
+  <si>
+    <t>Я027358</t>
+  </si>
+  <si>
+    <t>AD-220120-AzaliyaOSN-8</t>
+  </si>
+  <si>
+    <t>Азалия Бязь набив. 220 см рис.23162-1</t>
+  </si>
+  <si>
+    <t>Я021454</t>
+  </si>
+  <si>
+    <t>AD-220120-SiestaOSN-8</t>
+  </si>
+  <si>
+    <t>Сиеста Бязь набивная 220см рис. 13198-1</t>
+  </si>
+  <si>
+    <t>Я024623</t>
+  </si>
+  <si>
+    <t>AD-220120-Astilba-8</t>
+  </si>
+  <si>
+    <t>Астильба Бязь набивная 220см рис. 13401-1</t>
+  </si>
+  <si>
+    <t>Я028057</t>
+  </si>
+  <si>
+    <t>AD-220120-ShyelkKOMP-8</t>
+  </si>
+  <si>
+    <t>Шёлк Комп.Бязь набивная 220см рис. 13158-1</t>
+  </si>
+  <si>
+    <t>Я024414</t>
+  </si>
+  <si>
+    <t>AD-220120-RodosOSN-8</t>
+  </si>
+  <si>
+    <t>Родос Бязь набивная 220см рис. 13045-1</t>
+  </si>
+  <si>
+    <t>Я021870</t>
+  </si>
+  <si>
+    <t>AD-220120-PreobrazhenieOSN-8</t>
+  </si>
+  <si>
+    <t>Преображение Бязь набивная 220см рис. 13269-1</t>
+  </si>
+  <si>
+    <t>Я025102</t>
+  </si>
+  <si>
+    <t>AD-220120-dzhoystikOSN-8</t>
+  </si>
+  <si>
+    <t>Джойстик Бязь набивная 220см рис. 13354-1</t>
+  </si>
+  <si>
+    <t>Я027357</t>
+  </si>
+  <si>
+    <t>AD-220120-ShikKOMP-8</t>
+  </si>
+  <si>
+    <t>Шик Комп.Бязь набив. 220 см рис.12399-1</t>
+  </si>
+  <si>
+    <t>Я014922</t>
+  </si>
+  <si>
+    <t>AD-220120-TokioKOMP-8</t>
+  </si>
+  <si>
+    <t>Токио Комп. Бязь набивная ш. 220см рис. 13209-1</t>
+  </si>
+  <si>
+    <t>Я024493</t>
+  </si>
+  <si>
+    <t>AD-220120-GavanOSN-8</t>
+  </si>
+  <si>
+    <t>Гавань Бязь набивная 220см рис. 13239-1</t>
+  </si>
+  <si>
+    <t>Я024723</t>
+  </si>
+  <si>
+    <t>AD-220120-LorentseKOMP-8</t>
+  </si>
+  <si>
+    <t>Лоренце Комп.Бязь набивная 220см рис. 12556-2</t>
+  </si>
+  <si>
+    <t>Я022459</t>
+  </si>
+  <si>
+    <t>AD-220120-Krasotki-8</t>
+  </si>
+  <si>
+    <t>Красотки. Бязь набив. 220 см рис.8032-1</t>
+  </si>
+  <si>
+    <t>8032-1</t>
+  </si>
+  <si>
+    <t>AD-220120-KapigusiKOMP-8</t>
+  </si>
+  <si>
+    <t>Капигуси Комп.Бязь набивная 220см рис. 13413-2</t>
+  </si>
+  <si>
+    <t>Я028130</t>
+  </si>
+  <si>
+    <t>AD-220120-SnegiriOSN-8</t>
+  </si>
+  <si>
+    <t>Снегири Бязь набивная 220см рис. 12976-1</t>
+  </si>
+  <si>
+    <t>Я020689</t>
+  </si>
+  <si>
+    <t>AD-220120-GeyshaOSN-8</t>
+  </si>
+  <si>
+    <t>Гейша Бязь набив. 220 см рис.11847-1</t>
+  </si>
+  <si>
+    <t>Я011172</t>
+  </si>
+  <si>
+    <t>AD-220120-GeyshaKOMP-8</t>
+  </si>
+  <si>
+    <t>Гейша Комп.Бязь набив. 220 см рис.11847-2</t>
+  </si>
+  <si>
+    <t>Я011173</t>
+  </si>
+  <si>
+    <t>AD-220120-ElbrusOSN-8</t>
+  </si>
+  <si>
+    <t>Эльбрус. Бязь набив. 220 см рис.11887-1</t>
+  </si>
+  <si>
+    <t>Я011449</t>
+  </si>
+  <si>
+    <t>AD-220120-PegasOSN-8</t>
+  </si>
+  <si>
+    <t>Пегас Бязь набивная 220см рис. 13427-1</t>
+  </si>
+  <si>
+    <t>Я027931</t>
+  </si>
+  <si>
+    <t>AD-220120-IntonatsiyaOSN-8</t>
+  </si>
+  <si>
+    <t>Интонация Бязь набив. 220 см рис.11706-1</t>
+  </si>
+  <si>
+    <t>Я010190</t>
+  </si>
+  <si>
+    <t>AD-220120-SimfoniyaKOMP-8</t>
+  </si>
+  <si>
+    <t>Симфония Комп.Бязь набивная 220см рис. 13105-1</t>
+  </si>
+  <si>
+    <t>Я022536</t>
+  </si>
+  <si>
+    <t>AD-220120-EffektKOMP-8</t>
+  </si>
+  <si>
+    <t>Эффект Комп.Бязь набивная 220см рис. 13336-1</t>
+  </si>
+  <si>
+    <t>Я026577</t>
+  </si>
+  <si>
+    <t>AD-220120-NevesomostKOMP-8</t>
+  </si>
+  <si>
+    <t>Невесомость Комп.Бязь набивная 220см рис. 12942-1</t>
+  </si>
+  <si>
+    <t>Я020880</t>
+  </si>
+  <si>
+    <t>AD-220120-SonetOSN-8</t>
+  </si>
+  <si>
+    <t>Сонет Бязь набивная 220см рис. 12672-1</t>
+  </si>
+  <si>
+    <t>Я018788</t>
+  </si>
+  <si>
+    <t>AD-220120-SimvolUdachiOSN-8</t>
+  </si>
+  <si>
+    <t>Символ удачи. Бязь набив. 220 см рис.3755-1</t>
+  </si>
+  <si>
+    <t>3755-1</t>
+  </si>
+  <si>
+    <t>AD-220120-SherriKOMP-8</t>
+  </si>
+  <si>
+    <t>Шерри Комп.Бязь набивная 220см рис. 13364-1</t>
+  </si>
+  <si>
+    <t>Я027242</t>
+  </si>
+  <si>
+    <t>AD-220120-SimvolUdachiKOMP-8</t>
+  </si>
+  <si>
+    <t>Символ удачи Комп.Бязь набив. 220 см рис.12741-1</t>
+  </si>
+  <si>
+    <t>Я020975</t>
+  </si>
+  <si>
+    <t>AD-220120-VishiKOMP-8</t>
+  </si>
+  <si>
+    <t>Виши Комп.Бязь набивная 220см рис. 12710-1</t>
+  </si>
+  <si>
+    <t>Я018436</t>
+  </si>
+  <si>
+    <t>AD-220120-UltramarinKOMP-8</t>
+  </si>
+  <si>
+    <t>Ультрамарин Комп.Бязь набивная 220см рис. 13211-1</t>
+  </si>
+  <si>
+    <t>Я024646</t>
+  </si>
+  <si>
+    <t>AD-220120-TokioOSN-8</t>
+  </si>
+  <si>
+    <t>Токио Бязь набивная ш. 220см рис. 13208-1</t>
+  </si>
+  <si>
+    <t>Я024492</t>
+  </si>
+  <si>
+    <t>AD-220120-MagnoliyaOSN-8</t>
+  </si>
+  <si>
+    <t>Магнолия Бязь набивная 220см рис. 13273-1</t>
+  </si>
+  <si>
+    <t>Я025103</t>
+  </si>
+  <si>
+    <t>AD-220120-PalermoKOMP-8</t>
+  </si>
+  <si>
+    <t>Палермо Комп. Бязь набив. 220 см рис.10929-1</t>
+  </si>
+  <si>
+    <t>10929-1</t>
+  </si>
+  <si>
+    <t>AD-220120-PolyankaKOMP-8</t>
+  </si>
+  <si>
+    <t>Полянка Комп. Бязь набив. 220 см рис.13247-1</t>
+  </si>
+  <si>
+    <t>Я024891</t>
+  </si>
+  <si>
+    <t>AD-220120-AntuanettaKOMP-8</t>
+  </si>
+  <si>
+    <t>Антуанетта Комп.Бязь набивная 220см рис. 13307-1</t>
+  </si>
+  <si>
+    <t>Я026265</t>
+  </si>
+  <si>
+    <t>AD-220120-SiestaKOMP-8</t>
+  </si>
+  <si>
+    <t>Сиеста Комп.Бязь набивная 220см рис. 13199-1</t>
+  </si>
+  <si>
+    <t>Я024624</t>
+  </si>
+  <si>
+    <t>AD-220120-PolyankaOSN-8</t>
+  </si>
+  <si>
+    <t>Полянка Бязь набивная 220см рис. 13246-1</t>
+  </si>
+  <si>
+    <t>Я024890</t>
+  </si>
+  <si>
+    <t>AD-220120-PegasKOMP-8</t>
+  </si>
+  <si>
+    <t>Пегас Комп.Бязь набивная 220см рис. 13428-1</t>
+  </si>
+  <si>
+    <t>Я027932</t>
+  </si>
+  <si>
+    <t>AD-220120-ZhenevaKOMP-8</t>
+  </si>
+  <si>
+    <t>Женева Комп Бязь набив. 220 см рис.11141-1</t>
+  </si>
+  <si>
+    <t>Я003490</t>
+  </si>
+  <si>
+    <t>AD-220120-CharovnitsaKOMP-8</t>
+  </si>
+  <si>
+    <t>Чаровница Комп.Бязь набивная 220см рис. 13139-1</t>
+  </si>
+  <si>
+    <t>Я022956</t>
+  </si>
+  <si>
+    <t>AD-220120-ValsOSN-8</t>
+  </si>
+  <si>
+    <t>Вальс Бязь набив. 220 см рис.12612-1</t>
+  </si>
+  <si>
+    <t>Я018015</t>
+  </si>
+  <si>
+    <t>AD-220120-ModistkaKOMP-8</t>
+  </si>
+  <si>
+    <t>Модистка Комп.Бязь набивная 220см рис. 13341-1</t>
+  </si>
+  <si>
+    <t>Я026807</t>
+  </si>
+  <si>
+    <t>AD-220120-SevernayaKoronaKOMP-8</t>
+  </si>
+  <si>
+    <t>Северная корона Комп.Бязь набивная 220см рис. 13043-1</t>
+  </si>
+  <si>
+    <t>Я024644</t>
+  </si>
+  <si>
+    <t>AD-220120-KotovasiyaOSN-8</t>
+  </si>
+  <si>
+    <t>Котовасия Бязь набивная 220см рис. 13049-1</t>
+  </si>
+  <si>
+    <t>Я021521</t>
+  </si>
+  <si>
+    <t>AD-220120-VishneviySadKOMP-8</t>
+  </si>
+  <si>
+    <t>Вишневый сад Комп.Бязь набивная 220см рис. 13083-1</t>
+  </si>
+  <si>
+    <t>Я022013</t>
+  </si>
+  <si>
+    <t>AD-220120-AlbertKOMP-8</t>
+  </si>
+  <si>
+    <t>Альберт Комп.Бязь набивная 220см рис. 12868-1</t>
+  </si>
+  <si>
+    <t>Я019908</t>
+  </si>
+  <si>
+    <t>AD-220120-BelkantoOSN-8</t>
+  </si>
+  <si>
+    <t>Бельканто Бязь набивная 220см рис. 13134-1</t>
+  </si>
+  <si>
+    <t>Я022935</t>
+  </si>
+  <si>
+    <t>AD-220120-SimfoniyaOSN-8</t>
+  </si>
+  <si>
+    <t>Симфония Бязь набивная 220см рис. 13104-1</t>
+  </si>
+  <si>
+    <t>Я022535</t>
+  </si>
+  <si>
+    <t>AD-220120-SenorOSN-8</t>
+  </si>
+  <si>
+    <t>Сеньор Бязь набив. 220 см рис.12315-1</t>
+  </si>
+  <si>
+    <t>Я015089</t>
+  </si>
+  <si>
+    <t>AD-220120-PismoTatyanyOSN-8</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>AD-220120-GavanKOMP-8</t>
+  </si>
+  <si>
+    <t>Гавань Комп. Бязь набив. 220 см рис.13240-1</t>
+  </si>
+  <si>
+    <t>Я024724</t>
+  </si>
+  <si>
+    <t>AD-220120-KeniyaOSN-8</t>
+  </si>
+  <si>
+    <t>Кения Бязь набивная 220см рис. 13068-1</t>
+  </si>
+  <si>
+    <t>Я022819</t>
+  </si>
+  <si>
+    <t>AD-220120-YasminaKOMP-8</t>
+  </si>
+  <si>
+    <t>Ясмина Комп. Бязь набив. 220 см рис.13276-1</t>
+  </si>
+  <si>
+    <t>Я025107</t>
+  </si>
+  <si>
+    <t>AD-220120-GarmoniyaKOMP-8</t>
+  </si>
+  <si>
+    <t>Гармония Комп.Бязь набивная 220см рис. 13131-1</t>
+  </si>
+  <si>
+    <t>Я022879</t>
+  </si>
+  <si>
+    <t>AD-220120-Vilen-8</t>
+  </si>
+  <si>
+    <t>Вилен Бязь набивная 220см рис. 13399-1</t>
+  </si>
+  <si>
+    <t>Я028127</t>
+  </si>
+  <si>
+    <t>AD-150120-Klaviatura-8</t>
+  </si>
+  <si>
+    <t>Клавиатура. Бязь набив. 150 см рис.4484-1</t>
+  </si>
+  <si>
+    <t>4484-1</t>
+  </si>
+  <si>
+    <t>AD-150120-IgraKomp-8</t>
+  </si>
+  <si>
+    <t>Игра Комп. Бязь набивная 150 см. рис.12973-1</t>
+  </si>
+  <si>
+    <t>Я021814</t>
+  </si>
+  <si>
+    <t>AD-150120-LegolendKomp-8</t>
+  </si>
+  <si>
+    <t>Леголэнд Комп. Бязь набивная 150 см. рис.12852-1</t>
+  </si>
+  <si>
+    <t>Я019991</t>
+  </si>
+  <si>
+    <t>AD-150120-AvtodromKomp-8</t>
+  </si>
+  <si>
+    <t>Автодром Компаньон. Бязь набив. 150 см рис.23145-1</t>
+  </si>
+  <si>
+    <t>Я021064</t>
+  </si>
+  <si>
+    <t>AD-220120-CharovnitsaOSN-8</t>
+  </si>
+  <si>
+    <t>Чаровница Бязь набивная 220см рис. 13138-1</t>
+  </si>
+  <si>
+    <t>Я022955</t>
+  </si>
+  <si>
+    <t>AD-220120-SmaylKOMP-8</t>
+  </si>
+  <si>
+    <t>Смайл Комп.Бязь набивная 220см рис. 13358-1</t>
+  </si>
+  <si>
+    <t>Я026914</t>
+  </si>
+  <si>
+    <t>AD-220120-KeniyaKOMP-8</t>
+  </si>
+  <si>
+    <t>Кения Комп.Бязь набивная 220см рис. 13069-1-1</t>
+  </si>
+  <si>
+    <t>Я022820</t>
+  </si>
+  <si>
+    <t>AD-220120-TerriOSN-8</t>
+  </si>
+  <si>
+    <t>Терри Бязь набивная 220см рис. 13424-1</t>
+  </si>
+  <si>
+    <t>Я027973</t>
+  </si>
+  <si>
+    <t>AD-150120-LegolendOsn-8</t>
+  </si>
+  <si>
+    <t>Леголэнд. Бязь набив. 150 см рис.12851-1</t>
+  </si>
+  <si>
+    <t>Я019990</t>
+  </si>
+  <si>
+    <t>AD-150120-PtashkaOsn-8</t>
+  </si>
+  <si>
+    <t>Пташка Бязь набив. 150 см рис.12832-1</t>
+  </si>
+  <si>
+    <t>Я022369</t>
+  </si>
+  <si>
+    <t>AD-220120-LorentseOSN-8</t>
+  </si>
+  <si>
+    <t>Лоренце Бязь набивная 220см рис. 13047-1</t>
+  </si>
+  <si>
+    <t>Я022458</t>
+  </si>
+  <si>
+    <t>AD-220120-SaraKOMP-8</t>
+  </si>
+  <si>
+    <t>Сара Комп.Бязь набив. 220 см рис.13253-1</t>
+  </si>
+  <si>
+    <t>Я024826</t>
+  </si>
+  <si>
+    <t>AD-150120-PtashkaKomp-8</t>
+  </si>
+  <si>
+    <t>Пташка Комп. Бязь набивная 150 см. рис.12833-1</t>
+  </si>
+  <si>
+    <t>Я022370</t>
+  </si>
+  <si>
+    <t>AD-150120-MotorchikOsn-8</t>
+  </si>
+  <si>
+    <t>Моторчик Бязь набив. 150 см рис.11410-1</t>
+  </si>
+  <si>
+    <t>Я006933</t>
+  </si>
+  <si>
+    <t>AD-150120-Khokkey-8</t>
+  </si>
+  <si>
+    <t>Хоккей Комп.Бязь набив. 150 см рис.12085-1</t>
+  </si>
+  <si>
+    <t>Я013767</t>
+  </si>
+  <si>
+    <t>AD-150120-Detstvo-8</t>
+  </si>
+  <si>
+    <t>Детство Комп. Бязь набив. 150 см рис.11300-1</t>
+  </si>
+  <si>
+    <t>Я005302</t>
+  </si>
+  <si>
+    <t>AD-150120-PenaltiOsn-8</t>
+  </si>
+  <si>
+    <t>Пенальти Бязь набив. 150 см рис. 23140-1</t>
+  </si>
+  <si>
+    <t>Я021062</t>
+  </si>
+  <si>
+    <t>AD-150120-GoshaOsn-8</t>
+  </si>
+  <si>
+    <t>Гоша Бязь набив. 150 см рис.12838-1</t>
+  </si>
+  <si>
+    <t>Я020278</t>
+  </si>
+  <si>
+    <t>AD-150120-UlyetnyemishkiOsn-8</t>
+  </si>
+  <si>
+    <t>Улётные мишки Бязь набив. 150 см рис.12644-1</t>
+  </si>
+  <si>
+    <t>Я018141</t>
+  </si>
+  <si>
+    <t>AD-150120-IgraOsn-8</t>
+  </si>
+  <si>
+    <t>Игра Бязь набивная 150 см. рис. 12972-1</t>
+  </si>
+  <si>
+    <t>Я021813</t>
+  </si>
+  <si>
+    <t>AD-150120-BarashkiOsn-8</t>
+  </si>
+  <si>
+    <t>Барашки Бязь набив. 150 см рис.13248-1</t>
+  </si>
+  <si>
+    <t>Я024898</t>
+  </si>
+  <si>
+    <t>AD-150120-UlyetnyemishkiKomp-8</t>
+  </si>
+  <si>
+    <t>AD-150120-MiniVecherinkaKomp-8</t>
+  </si>
+  <si>
+    <t>Мини вечеринка Комп. Бязь набивная 150 см. рис.12731-1</t>
+  </si>
+  <si>
+    <t>Я018653</t>
+  </si>
+  <si>
+    <t>AD-150120-PenaltiKomp-8</t>
+  </si>
+  <si>
+    <t>AD-150120-ImidzhKomp-8</t>
+  </si>
+  <si>
+    <t>Имидж Комп. Бязь набивная 150 см. рис.12922-1</t>
+  </si>
+  <si>
+    <t>Я020330</t>
+  </si>
+  <si>
+    <t>AD-150120-AvtodromOsn-8</t>
+  </si>
+  <si>
+    <t>Автодром Бязь набив. 150 см рис. 23144-1</t>
+  </si>
+  <si>
+    <t>Я021061</t>
+  </si>
+  <si>
+    <t>AD-220120-SnegiriKOMP-8</t>
+  </si>
+  <si>
+    <t>Снегири Комп.Бязь набивная 220см рис. 12977-1</t>
+  </si>
+  <si>
+    <t>Я020690</t>
+  </si>
+  <si>
+    <t>AD-220120-RomansKOMP-8</t>
+  </si>
+  <si>
+    <t>Романс Комп.Бязь набивная 220см рис. 12831-1</t>
+  </si>
+  <si>
+    <t>Я019946</t>
+  </si>
+  <si>
+    <t>AD-150120-Dinopark-8</t>
+  </si>
+  <si>
+    <t>Динопарк Комп. Бязь набив. 150 см рис.11662-1</t>
+  </si>
+  <si>
+    <t>Я009871</t>
+  </si>
+  <si>
+    <t>AD-150120-BarashkiKomp-8</t>
+  </si>
+  <si>
+    <t>Барашки Комп. Бязь набивная 150 см. рис.13249-1</t>
+  </si>
+  <si>
+    <t>Я024899</t>
+  </si>
+  <si>
+    <t>AD-220120-SonetKOMP-8</t>
+  </si>
+  <si>
+    <t>Сонет Комп.Бязь набивная 220см рис. 12673-1</t>
+  </si>
+  <si>
+    <t>Я018789</t>
+  </si>
+  <si>
+    <t>AD-150120-MorskoyBoyKomp-8</t>
+  </si>
+  <si>
+    <t>Морской бой Комп. Бязь набивная 150 см. рис.12721-1</t>
+  </si>
+  <si>
+    <t>Я018757</t>
+  </si>
+  <si>
+    <t>AD-150120-NaOpushkeOsn-8</t>
+  </si>
+  <si>
+    <t>На опушке Бязь набив. 150 см рис.13436-1</t>
+  </si>
+  <si>
+    <t>Я028072</t>
+  </si>
+  <si>
+    <t>AD-150120-ZamurchatelZhiznKomp-8</t>
+  </si>
+  <si>
+    <t>Замурчательная жизнь Компаньон. Бязь набив. 150 см рис.23170-1</t>
+  </si>
+  <si>
+    <t>Я022580</t>
+  </si>
+  <si>
+    <t>AD-150120-ZamurchatelZhiznOsn-8</t>
+  </si>
+  <si>
+    <t>Замурчательная жизнь Бязь набив. 150 см рис.12610-1</t>
+  </si>
+  <si>
+    <t>Я017743</t>
+  </si>
+  <si>
+    <t>AD-220120-PalermoOSN-8</t>
+  </si>
+  <si>
+    <t>Палермо. Бязь набив. 220 см рис.10928-1</t>
+  </si>
+  <si>
+    <t>10928-1</t>
+  </si>
+  <si>
+    <t>AD-220120-MurritoOSN-8</t>
+  </si>
+  <si>
+    <t>Муррито Бязь набивная 220см рис. 13288-1</t>
+  </si>
+  <si>
+    <t>Я026183</t>
+  </si>
+  <si>
+    <t>AD-220120-PreobrazhenieKOMP-8</t>
+  </si>
+  <si>
+    <t>Преображение Комп. Бязь набив. 220 см рис.13270-1</t>
+  </si>
+  <si>
+    <t>Я025105</t>
+  </si>
+  <si>
+    <t>AD-220120-MayronKOMP-8</t>
+  </si>
+  <si>
+    <t>Майрон Комп.Бязь набивная 220см рис. 13023-1</t>
+  </si>
+  <si>
+    <t>Я021093</t>
+  </si>
+  <si>
+    <t>AD-150120-GoshaKomp-8</t>
+  </si>
+  <si>
+    <t>Гоша Комп. Бязь набивная 150 см. рис.12839-1</t>
+  </si>
+  <si>
+    <t>Я020279</t>
+  </si>
+  <si>
+    <t>AD-150120-ImidzhOsn-8</t>
+  </si>
+  <si>
+    <t>Имидж Бязь набивная 150 см. рис. 12921-1</t>
+  </si>
+  <si>
+    <t>Я020328</t>
+  </si>
+  <si>
+    <t>AD-150120-Khvostiki-8</t>
+  </si>
+  <si>
+    <t>Хвостики. Комп.Бязь набив. 150 см рис.11376-1</t>
+  </si>
+  <si>
+    <t>Я006379</t>
+  </si>
+  <si>
+    <t>AD-150120-Stroitel-8</t>
+  </si>
+  <si>
+    <t>Строитель Бязь набив. 150 см рис.12365-1</t>
+  </si>
+  <si>
+    <t>Я014866</t>
+  </si>
+  <si>
+    <t>AD-150120-MorskoyBoyOsn-8</t>
+  </si>
+  <si>
+    <t>Морской бой. Бязь набив. 150 см рис.12720-1</t>
+  </si>
+  <si>
+    <t>Я018756</t>
+  </si>
+  <si>
+    <t>AD-150120-KolobokOsn-8</t>
+  </si>
+  <si>
+    <t>Колобок. Бязь набивная 150 см. рис. 12872-1</t>
+  </si>
+  <si>
+    <t>Я019900</t>
+  </si>
+  <si>
+    <t>AD-220120-TsvetokZhelaniyOSN-8</t>
+  </si>
+  <si>
+    <t>Цветок желаний Бязь набив. 220 см рис.12320-1</t>
+  </si>
+  <si>
+    <t>Я015036</t>
+  </si>
+  <si>
+    <t>AD-220120-BelyeTsveti-8</t>
+  </si>
+  <si>
+    <t>Белые цветы Бязь набивная 220см рис. 13066-1</t>
+  </si>
+  <si>
+    <t>Я021620</t>
+  </si>
+  <si>
+    <t>AD-150120-KolobokKomp-8</t>
+  </si>
+  <si>
+    <t>Колобок Комп. Бязь набивная 150 см. рис.12873-1</t>
+  </si>
+  <si>
+    <t>Я019901</t>
+  </si>
+  <si>
+    <t>AD-150120-MotorchikKomp-8</t>
+  </si>
+  <si>
+    <t>Моторчик Комп. Бязь набивная 150 см. рис.11411-1</t>
+  </si>
+  <si>
+    <t>Я006934</t>
+  </si>
+  <si>
+    <t>AD-150120-MiniVecherinkaOsn-8</t>
+  </si>
+  <si>
+    <t>Мини вечеринка Бязь набивная 150 см. рис. 12730-1</t>
+  </si>
+  <si>
+    <t>Я018652</t>
+  </si>
+  <si>
+    <t>AD-150120-NaOpushkeKomp-8</t>
+  </si>
+  <si>
+    <t>На опушке Комп. Бязь набивная 150 см. рис.13437-1</t>
+  </si>
+  <si>
+    <t>Я028073</t>
   </si>
 </sst>
 </file>
@@ -13209,4 +14572,2150 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D153"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="32.5" customWidth="1"/>
+    <col min="2" max="2" width="50.75" customWidth="1"/>
+    <col min="3" max="3" width="16.125" customWidth="1"/>
+    <col min="4" max="4" width="21" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="5" t="s">
+        <v>1512</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1513</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="D1">
+        <v>2045411146990</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="5" t="s">
+        <v>1515</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1516</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1517</v>
+      </c>
+      <c r="D2">
+        <v>2045411147553</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="5" t="s">
+        <v>1518</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1519</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1520</v>
+      </c>
+      <c r="D3">
+        <v>2045411146952</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="5" t="s">
+        <v>1521</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1522</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1523</v>
+      </c>
+      <c r="D4">
+        <v>2045411146860</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="5" t="s">
+        <v>1524</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1525</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1526</v>
+      </c>
+      <c r="D5">
+        <v>2045411147409</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="5" t="s">
+        <v>1527</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1528</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1529</v>
+      </c>
+      <c r="D6">
+        <v>2045411147348</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="5" t="s">
+        <v>1530</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1531</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1532</v>
+      </c>
+      <c r="D7">
+        <v>2045411146693</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="5" t="s">
+        <v>1533</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1534</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D8">
+        <v>2045411146969</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="5" t="s">
+        <v>1536</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1537</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1538</v>
+      </c>
+      <c r="D9">
+        <v>2045411146747</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="5" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1540</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1541</v>
+      </c>
+      <c r="D10">
+        <v>2045411146785</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="5" t="s">
+        <v>1542</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1544</v>
+      </c>
+      <c r="D11">
+        <v>2045411147027</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="5" t="s">
+        <v>1545</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1546</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1547</v>
+      </c>
+      <c r="D12">
+        <v>2045411147263</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="5" t="s">
+        <v>1548</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1549</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D13">
+        <v>2045411146303</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="5" t="s">
+        <v>1551</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1552</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1553</v>
+      </c>
+      <c r="D14">
+        <v>2045411146808</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="5" t="s">
+        <v>1554</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1555</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1556</v>
+      </c>
+      <c r="D15">
+        <v>2045411146815</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="5" t="s">
+        <v>1557</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1559</v>
+      </c>
+      <c r="D16">
+        <v>2045411147102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="5" t="s">
+        <v>1560</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1561</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1562</v>
+      </c>
+      <c r="D17">
+        <v>2045411146778</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="5" t="s">
+        <v>1563</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1564</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1565</v>
+      </c>
+      <c r="D18">
+        <v>2045411147041</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="5" t="s">
+        <v>1566</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1567</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1568</v>
+      </c>
+      <c r="D19">
+        <v>2045411146259</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="5" t="s">
+        <v>1569</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1570</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1571</v>
+      </c>
+      <c r="D20">
+        <v>2045411146914</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="5" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1573</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1574</v>
+      </c>
+      <c r="D21">
+        <v>2045411146709</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="5" t="s">
+        <v>1575</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1577</v>
+      </c>
+      <c r="D22">
+        <v>2045411146334</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="5" t="s">
+        <v>1578</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1579</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1580</v>
+      </c>
+      <c r="D23">
+        <v>2045411147263</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="5" t="s">
+        <v>1581</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1582</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1583</v>
+      </c>
+      <c r="D24">
+        <v>2045411146983</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="5" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1585</v>
+      </c>
+      <c r="C25" t="s">
+        <v>1586</v>
+      </c>
+      <c r="D25">
+        <v>2045411147232</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="5" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1588</v>
+      </c>
+      <c r="C26" t="s">
+        <v>1589</v>
+      </c>
+      <c r="D26">
+        <v>2045411147256</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="5" t="s">
+        <v>1590</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1591</v>
+      </c>
+      <c r="C27" t="s">
+        <v>1592</v>
+      </c>
+      <c r="D27">
+        <v>2045411146877</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="5" t="s">
+        <v>1593</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1594</v>
+      </c>
+      <c r="C28" t="s">
+        <v>1595</v>
+      </c>
+      <c r="D28">
+        <v>2045411146853</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="5" t="s">
+        <v>1596</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1597</v>
+      </c>
+      <c r="C29" t="s">
+        <v>1598</v>
+      </c>
+      <c r="D29">
+        <v>2045411146358</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="5" t="s">
+        <v>1599</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1600</v>
+      </c>
+      <c r="C30" t="s">
+        <v>1601</v>
+      </c>
+      <c r="D30">
+        <v>2045411146716</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="5" t="s">
+        <v>1602</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1603</v>
+      </c>
+      <c r="C31" t="s">
+        <v>1604</v>
+      </c>
+      <c r="D31">
+        <v>2045411147423</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="5" t="s">
+        <v>1605</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1606</v>
+      </c>
+      <c r="C32" t="s">
+        <v>1607</v>
+      </c>
+      <c r="D32">
+        <v>2045411147010</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="5" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1609</v>
+      </c>
+      <c r="C33" t="s">
+        <v>1610</v>
+      </c>
+      <c r="D33">
+        <v>2045411147065</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="5" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1612</v>
+      </c>
+      <c r="C34" t="s">
+        <v>1613</v>
+      </c>
+      <c r="D34">
+        <v>2045411147454</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="5" t="s">
+        <v>1614</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1615</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1616</v>
+      </c>
+      <c r="D35">
+        <v>2045411147140</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="5" t="s">
+        <v>1617</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1618</v>
+      </c>
+      <c r="C36" t="s">
+        <v>1619</v>
+      </c>
+      <c r="D36">
+        <v>2045411147058</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="5" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1621</v>
+      </c>
+      <c r="C37" t="s">
+        <v>1622</v>
+      </c>
+      <c r="D37">
+        <v>2045411147478</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="5" t="s">
+        <v>1623</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1624</v>
+      </c>
+      <c r="C38" t="s">
+        <v>1625</v>
+      </c>
+      <c r="D38">
+        <v>2045411147164</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="5" t="s">
+        <v>1626</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1627</v>
+      </c>
+      <c r="C39" t="s">
+        <v>1628</v>
+      </c>
+      <c r="D39">
+        <v>2045411146372</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="5" t="s">
+        <v>1629</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1630</v>
+      </c>
+      <c r="C40" t="s">
+        <v>1631</v>
+      </c>
+      <c r="D40">
+        <v>2045411147447</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="5" t="s">
+        <v>1632</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1633</v>
+      </c>
+      <c r="C41" t="s">
+        <v>1634</v>
+      </c>
+      <c r="D41">
+        <v>2045411147126</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="5" t="s">
+        <v>1635</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1636</v>
+      </c>
+      <c r="C42" t="s">
+        <v>1637</v>
+      </c>
+      <c r="D42">
+        <v>2045411146471</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="5" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1639</v>
+      </c>
+      <c r="C43" t="s">
+        <v>1640</v>
+      </c>
+      <c r="D43">
+        <v>2045411146907</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="5" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1642</v>
+      </c>
+      <c r="C44" t="s">
+        <v>1643</v>
+      </c>
+      <c r="D44">
+        <v>2045411147089</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="5" t="s">
+        <v>1644</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1645</v>
+      </c>
+      <c r="C45" t="s">
+        <v>1646</v>
+      </c>
+      <c r="D45">
+        <v>2045411146921</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1648</v>
+      </c>
+      <c r="C46" t="s">
+        <v>1649</v>
+      </c>
+      <c r="D46">
+        <v>2045411147034</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1651</v>
+      </c>
+      <c r="C47" t="s">
+        <v>1652</v>
+      </c>
+      <c r="D47">
+        <v>2045411147249</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="5" t="s">
+        <v>1653</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1654</v>
+      </c>
+      <c r="C48" t="s">
+        <v>1655</v>
+      </c>
+      <c r="D48">
+        <v>2045411146280</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="5" t="s">
+        <v>1656</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1657</v>
+      </c>
+      <c r="C49" t="s">
+        <v>1658</v>
+      </c>
+      <c r="D49">
+        <v>2045411147157</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="5" t="s">
+        <v>1659</v>
+      </c>
+      <c r="B50" t="s">
+        <v>1660</v>
+      </c>
+      <c r="C50" t="s">
+        <v>1661</v>
+      </c>
+      <c r="D50">
+        <v>2045411147218</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="5" t="s">
+        <v>1662</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1663</v>
+      </c>
+      <c r="C51" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D51">
+        <v>2045411147492</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="5" t="s">
+        <v>1665</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1666</v>
+      </c>
+      <c r="C52" t="s">
+        <v>1667</v>
+      </c>
+      <c r="D52">
+        <v>2045411146792</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="5" t="s">
+        <v>1668</v>
+      </c>
+      <c r="B53" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C53" t="s">
+        <v>1670</v>
+      </c>
+      <c r="D53">
+        <v>2045411147331</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="5" t="s">
+        <v>1671</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1672</v>
+      </c>
+      <c r="C54" t="s">
+        <v>1673</v>
+      </c>
+      <c r="D54">
+        <v>2045411146488</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="5" t="s">
+        <v>1674</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1675</v>
+      </c>
+      <c r="C55" t="s">
+        <v>1676</v>
+      </c>
+      <c r="D55">
+        <v>2045411146891</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="5" t="s">
+        <v>1677</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1678</v>
+      </c>
+      <c r="C56" t="s">
+        <v>1679</v>
+      </c>
+      <c r="D56">
+        <v>2045411147539</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="5" t="s">
+        <v>1680</v>
+      </c>
+      <c r="B57" t="s">
+        <v>1681</v>
+      </c>
+      <c r="C57" t="s">
+        <v>1682</v>
+      </c>
+      <c r="D57">
+        <v>2045411147287</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="5" t="s">
+        <v>1683</v>
+      </c>
+      <c r="B58" t="s">
+        <v>1684</v>
+      </c>
+      <c r="C58" t="s">
+        <v>1685</v>
+      </c>
+      <c r="D58">
+        <v>2045411146945</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="5" t="s">
+        <v>1686</v>
+      </c>
+      <c r="B59" t="s">
+        <v>1687</v>
+      </c>
+      <c r="C59" t="s">
+        <v>1688</v>
+      </c>
+      <c r="D59">
+        <v>2045411147294</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="5" t="s">
+        <v>1689</v>
+      </c>
+      <c r="B60" t="s">
+        <v>1690</v>
+      </c>
+      <c r="C60" t="s">
+        <v>1691</v>
+      </c>
+      <c r="D60">
+        <v>2045411147591</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="5" t="s">
+        <v>1692</v>
+      </c>
+      <c r="B61" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C61" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D61">
+        <v>2045411146754</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="5" t="s">
+        <v>1695</v>
+      </c>
+      <c r="B62" t="s">
+        <v>1696</v>
+      </c>
+      <c r="C62" t="s">
+        <v>1697</v>
+      </c>
+      <c r="D62">
+        <v>2045411146938</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="5" t="s">
+        <v>1698</v>
+      </c>
+      <c r="B63" t="s">
+        <v>1699</v>
+      </c>
+      <c r="C63" t="s">
+        <v>1700</v>
+      </c>
+      <c r="D63">
+        <v>2045411146846</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="5" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B64" t="s">
+        <v>1702</v>
+      </c>
+      <c r="C64" t="s">
+        <v>1703</v>
+      </c>
+      <c r="D64">
+        <v>2045411147645</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="5" t="s">
+        <v>1704</v>
+      </c>
+      <c r="B65" t="s">
+        <v>1705</v>
+      </c>
+      <c r="C65" t="s">
+        <v>1706</v>
+      </c>
+      <c r="D65">
+        <v>2045411146662</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="5" t="s">
+        <v>1707</v>
+      </c>
+      <c r="B66" t="s">
+        <v>1708</v>
+      </c>
+      <c r="C66" t="s">
+        <v>1709</v>
+      </c>
+      <c r="D66">
+        <v>2045411147546</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="5" t="s">
+        <v>1710</v>
+      </c>
+      <c r="B67" t="s">
+        <v>1711</v>
+      </c>
+      <c r="C67" t="s">
+        <v>1712</v>
+      </c>
+      <c r="D67">
+        <v>2045411146884</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="5" t="s">
+        <v>1713</v>
+      </c>
+      <c r="B68" t="s">
+        <v>1714</v>
+      </c>
+      <c r="C68" t="s">
+        <v>1715</v>
+      </c>
+      <c r="D68">
+        <v>2045411147300</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="5" t="s">
+        <v>1716</v>
+      </c>
+      <c r="B69" t="s">
+        <v>1717</v>
+      </c>
+      <c r="C69" t="s">
+        <v>1718</v>
+      </c>
+      <c r="D69">
+        <v>2045411147379</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" s="5" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B70" t="s">
+        <v>1720</v>
+      </c>
+      <c r="C70" t="s">
+        <v>1721</v>
+      </c>
+      <c r="D70">
+        <v>2045411146440</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" s="5" t="s">
+        <v>1722</v>
+      </c>
+      <c r="B71" t="s">
+        <v>1723</v>
+      </c>
+      <c r="C71" t="s">
+        <v>1724</v>
+      </c>
+      <c r="D71">
+        <v>2045411147560</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" s="5" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B72" t="s">
+        <v>1726</v>
+      </c>
+      <c r="C72" t="s">
+        <v>1727</v>
+      </c>
+      <c r="D72">
+        <v>2045411147362</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" s="5" t="s">
+        <v>1728</v>
+      </c>
+      <c r="B73" t="s">
+        <v>1729</v>
+      </c>
+      <c r="C73" t="s">
+        <v>1730</v>
+      </c>
+      <c r="D73">
+        <v>2045411146686</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" s="5" t="s">
+        <v>1731</v>
+      </c>
+      <c r="B74" t="s">
+        <v>1732</v>
+      </c>
+      <c r="C74" t="s">
+        <v>1733</v>
+      </c>
+      <c r="D74">
+        <v>2045411147430</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" s="5" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B75" t="s">
+        <v>1735</v>
+      </c>
+      <c r="C75" t="s">
+        <v>1736</v>
+      </c>
+      <c r="D75">
+        <v>2045411147119</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" s="5" t="s">
+        <v>1737</v>
+      </c>
+      <c r="B76" t="s">
+        <v>1738</v>
+      </c>
+      <c r="C76" t="s">
+        <v>1739</v>
+      </c>
+      <c r="D76">
+        <v>2045411146822</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" s="5" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B77" t="s">
+        <v>1741</v>
+      </c>
+      <c r="C77" t="s">
+        <v>1742</v>
+      </c>
+      <c r="D77">
+        <v>2045411147393</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" s="5" t="s">
+        <v>1743</v>
+      </c>
+      <c r="B78" t="s">
+        <v>1744</v>
+      </c>
+      <c r="C78" t="s">
+        <v>1745</v>
+      </c>
+      <c r="D78">
+        <v>2045411147096</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" s="5" t="s">
+        <v>1746</v>
+      </c>
+      <c r="B79" t="s">
+        <v>1747</v>
+      </c>
+      <c r="C79" t="s">
+        <v>1748</v>
+      </c>
+      <c r="D79">
+        <v>2045411147201</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" s="5" t="s">
+        <v>1749</v>
+      </c>
+      <c r="B80" t="s">
+        <v>1750</v>
+      </c>
+      <c r="C80" t="s">
+        <v>1751</v>
+      </c>
+      <c r="D80">
+        <v>2045411146679</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="5" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B81" t="s">
+        <v>1753</v>
+      </c>
+      <c r="C81" t="s">
+        <v>1754</v>
+      </c>
+      <c r="D81">
+        <v>2045411147133</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" s="5" t="s">
+        <v>1755</v>
+      </c>
+      <c r="B82" t="s">
+        <v>1756</v>
+      </c>
+      <c r="C82" t="s">
+        <v>1757</v>
+      </c>
+      <c r="D82">
+        <v>2045411147270</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" s="5" t="s">
+        <v>1758</v>
+      </c>
+      <c r="B83" t="s">
+        <v>1759</v>
+      </c>
+      <c r="C83" t="s">
+        <v>1760</v>
+      </c>
+      <c r="D83">
+        <v>2045411147324</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" s="5" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B84" t="s">
+        <v>1762</v>
+      </c>
+      <c r="C84" t="s">
+        <v>1763</v>
+      </c>
+      <c r="D84">
+        <v>2045411147614</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" s="5" t="s">
+        <v>1764</v>
+      </c>
+      <c r="B85" t="s">
+        <v>1765</v>
+      </c>
+      <c r="C85" t="s">
+        <v>1766</v>
+      </c>
+      <c r="D85">
+        <v>2045411147461</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" s="5" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B86" t="s">
+        <v>1768</v>
+      </c>
+      <c r="C86" t="s">
+        <v>1769</v>
+      </c>
+      <c r="D86">
+        <v>2045411147072</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" s="5" t="s">
+        <v>1770</v>
+      </c>
+      <c r="B87" t="s">
+        <v>1771</v>
+      </c>
+      <c r="C87" t="s">
+        <v>1772</v>
+      </c>
+      <c r="D87">
+        <v>2045411147485</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" s="5" t="s">
+        <v>1773</v>
+      </c>
+      <c r="B88" t="s">
+        <v>1774</v>
+      </c>
+      <c r="C88" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D88">
+        <v>2045411146761</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" s="5" t="s">
+        <v>1776</v>
+      </c>
+      <c r="B89" t="s">
+        <v>1777</v>
+      </c>
+      <c r="C89" t="s">
+        <v>1778</v>
+      </c>
+      <c r="D89">
+        <v>2045411146402</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" s="5" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B90" t="s">
+        <v>1780</v>
+      </c>
+      <c r="C90" t="s">
+        <v>1781</v>
+      </c>
+      <c r="D90">
+        <v>2045411147577</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" s="5" t="s">
+        <v>1782</v>
+      </c>
+      <c r="B91" t="s">
+        <v>1783</v>
+      </c>
+      <c r="C91" t="s">
+        <v>1784</v>
+      </c>
+      <c r="D91">
+        <v>2045411147065</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" s="5" t="s">
+        <v>1785</v>
+      </c>
+      <c r="B92" t="s">
+        <v>1786</v>
+      </c>
+      <c r="C92" t="s">
+        <v>1787</v>
+      </c>
+      <c r="D92">
+        <v>2045411147621</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" s="5" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B93" t="s">
+        <v>1789</v>
+      </c>
+      <c r="C93" t="s">
+        <v>1790</v>
+      </c>
+      <c r="D93">
+        <v>2045411147416</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" s="5" t="s">
+        <v>1791</v>
+      </c>
+      <c r="B94" t="s">
+        <v>1792</v>
+      </c>
+      <c r="C94" t="s">
+        <v>1793</v>
+      </c>
+      <c r="D94">
+        <v>2045411147508</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" s="5" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B95" t="s">
+        <v>1795</v>
+      </c>
+      <c r="C95" t="s">
+        <v>1796</v>
+      </c>
+      <c r="D95">
+        <v>2045411147584</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" s="5" t="s">
+        <v>1797</v>
+      </c>
+      <c r="B96" t="s">
+        <v>1798</v>
+      </c>
+      <c r="C96" t="s">
+        <v>1799</v>
+      </c>
+      <c r="D96">
+        <v>2045411147386</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" s="5" t="s">
+        <v>1800</v>
+      </c>
+      <c r="B97" t="s">
+        <v>1801</v>
+      </c>
+      <c r="C97" t="s">
+        <v>1801</v>
+      </c>
+      <c r="D97">
+        <v>2045411146723</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" s="5" t="s">
+        <v>1802</v>
+      </c>
+      <c r="B98" t="s">
+        <v>1803</v>
+      </c>
+      <c r="C98" t="s">
+        <v>1804</v>
+      </c>
+      <c r="D98">
+        <v>2045411146730</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" s="5" t="s">
+        <v>1805</v>
+      </c>
+      <c r="B99" t="s">
+        <v>1806</v>
+      </c>
+      <c r="C99" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D99">
+        <v>2045411147355</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" s="5" t="s">
+        <v>1808</v>
+      </c>
+      <c r="B100" t="s">
+        <v>1809</v>
+      </c>
+      <c r="C100" t="s">
+        <v>1810</v>
+      </c>
+      <c r="D100">
+        <v>2045411147317</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" s="5" t="s">
+        <v>1811</v>
+      </c>
+      <c r="B101" t="s">
+        <v>1812</v>
+      </c>
+      <c r="C101" t="s">
+        <v>1813</v>
+      </c>
+      <c r="D101">
+        <v>2045411146617</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" s="5" t="s">
+        <v>1814</v>
+      </c>
+      <c r="B102" t="s">
+        <v>1815</v>
+      </c>
+      <c r="C102" t="s">
+        <v>1816</v>
+      </c>
+      <c r="D102">
+        <v>2045411146631</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" s="5" t="s">
+        <v>1817</v>
+      </c>
+      <c r="B103" t="s">
+        <v>1818</v>
+      </c>
+      <c r="C103" t="s">
+        <v>1819</v>
+      </c>
+      <c r="D103">
+        <v>2045413136395</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" s="5" t="s">
+        <v>1820</v>
+      </c>
+      <c r="B104" t="s">
+        <v>1821</v>
+      </c>
+      <c r="C104" t="s">
+        <v>1822</v>
+      </c>
+      <c r="D104">
+        <v>2045413135855</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" s="5" t="s">
+        <v>1823</v>
+      </c>
+      <c r="B105" t="s">
+        <v>1824</v>
+      </c>
+      <c r="C105" t="s">
+        <v>1825</v>
+      </c>
+      <c r="D105">
+        <v>2045413136494</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="5" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B106" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C106" t="s">
+        <v>1828</v>
+      </c>
+      <c r="D106">
+        <v>2045413135893</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="5" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B107" t="s">
+        <v>1830</v>
+      </c>
+      <c r="C107" t="s">
+        <v>1831</v>
+      </c>
+      <c r="D107">
+        <v>2045411146563</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" s="5" t="s">
+        <v>1832</v>
+      </c>
+      <c r="B108" t="s">
+        <v>1833</v>
+      </c>
+      <c r="C108" t="s">
+        <v>1834</v>
+      </c>
+      <c r="D108">
+        <v>2045411146648</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" s="5" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B109" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C109" t="s">
+        <v>1837</v>
+      </c>
+      <c r="D109">
+        <v>2045411146655</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" s="5" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B110" t="s">
+        <v>1839</v>
+      </c>
+      <c r="C110" t="s">
+        <v>1840</v>
+      </c>
+      <c r="D110">
+        <v>2045411146594</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="5" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B111" t="s">
+        <v>1842</v>
+      </c>
+      <c r="C111" t="s">
+        <v>1843</v>
+      </c>
+      <c r="D111">
+        <v>2045413136098</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="5" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B112" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C112" t="s">
+        <v>1846</v>
+      </c>
+      <c r="D112">
+        <v>2045413135817</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113" s="5" t="s">
+        <v>1847</v>
+      </c>
+      <c r="B113" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C113" t="s">
+        <v>1849</v>
+      </c>
+      <c r="D113">
+        <v>2045411146495</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114" s="5" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B114" t="s">
+        <v>1851</v>
+      </c>
+      <c r="C114" t="s">
+        <v>1852</v>
+      </c>
+      <c r="D114">
+        <v>2045411146570</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115" s="5" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B115" t="s">
+        <v>1854</v>
+      </c>
+      <c r="C115" t="s">
+        <v>1855</v>
+      </c>
+      <c r="D115">
+        <v>2045413136371</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116" s="5" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B116" t="s">
+        <v>1857</v>
+      </c>
+      <c r="C116" t="s">
+        <v>1858</v>
+      </c>
+      <c r="D116">
+        <v>2045413135800</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
+      <c r="A117" s="5" t="s">
+        <v>1859</v>
+      </c>
+      <c r="B117" t="s">
+        <v>1860</v>
+      </c>
+      <c r="C117" t="s">
+        <v>1861</v>
+      </c>
+      <c r="D117">
+        <v>2045413136081</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
+      <c r="A118" s="5" t="s">
+        <v>1862</v>
+      </c>
+      <c r="B118" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C118" t="s">
+        <v>1864</v>
+      </c>
+      <c r="D118">
+        <v>2045413135848</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
+      <c r="A119" s="5" t="s">
+        <v>1865</v>
+      </c>
+      <c r="B119" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C119" t="s">
+        <v>1867</v>
+      </c>
+      <c r="D119">
+        <v>2045413136333</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120" s="5" t="s">
+        <v>1868</v>
+      </c>
+      <c r="B120" t="s">
+        <v>1869</v>
+      </c>
+      <c r="C120" t="s">
+        <v>1870</v>
+      </c>
+      <c r="D120">
+        <v>2045413136463</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
+      <c r="A121" s="5" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B121" t="s">
+        <v>1872</v>
+      </c>
+      <c r="C121" t="s">
+        <v>1873</v>
+      </c>
+      <c r="D121">
+        <v>2045413136340</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4">
+      <c r="A122" s="5" t="s">
+        <v>1874</v>
+      </c>
+      <c r="B122" t="s">
+        <v>1875</v>
+      </c>
+      <c r="C122" t="s">
+        <v>1876</v>
+      </c>
+      <c r="D122">
+        <v>2045413136135</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
+      <c r="A123" s="5" t="s">
+        <v>1877</v>
+      </c>
+      <c r="B123" t="s">
+        <v>1878</v>
+      </c>
+      <c r="C123" t="s">
+        <v>1879</v>
+      </c>
+      <c r="D123">
+        <v>2045413135886</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
+      <c r="A124" s="5" t="s">
+        <v>1880</v>
+      </c>
+      <c r="D124">
+        <v>2045413135862</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4">
+      <c r="A125" s="5" t="s">
+        <v>1881</v>
+      </c>
+      <c r="B125" t="s">
+        <v>1882</v>
+      </c>
+      <c r="C125" t="s">
+        <v>1883</v>
+      </c>
+      <c r="D125">
+        <v>2045413136517</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
+      <c r="A126" s="5" t="s">
+        <v>1884</v>
+      </c>
+      <c r="D126">
+        <v>2045413136029</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
+      <c r="A127" s="5" t="s">
+        <v>1885</v>
+      </c>
+      <c r="B127" t="s">
+        <v>1886</v>
+      </c>
+      <c r="C127" t="s">
+        <v>1887</v>
+      </c>
+      <c r="D127">
+        <v>2045413136036</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4">
+      <c r="A128" s="5" t="s">
+        <v>1888</v>
+      </c>
+      <c r="B128" t="s">
+        <v>1889</v>
+      </c>
+      <c r="C128" t="s">
+        <v>1890</v>
+      </c>
+      <c r="D128">
+        <v>2045413136449</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4">
+      <c r="A129" s="5" t="s">
+        <v>1891</v>
+      </c>
+      <c r="B129" t="s">
+        <v>1892</v>
+      </c>
+      <c r="C129" t="s">
+        <v>1893</v>
+      </c>
+      <c r="D129">
+        <v>2045411146518</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
+      <c r="A130" s="5" t="s">
+        <v>1894</v>
+      </c>
+      <c r="B130" t="s">
+        <v>1895</v>
+      </c>
+      <c r="C130" t="s">
+        <v>1896</v>
+      </c>
+      <c r="D130">
+        <v>2045411146600</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4">
+      <c r="A131" s="5" t="s">
+        <v>1897</v>
+      </c>
+      <c r="B131" t="s">
+        <v>1898</v>
+      </c>
+      <c r="C131" t="s">
+        <v>1899</v>
+      </c>
+      <c r="D131">
+        <v>2045413135824</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
+      <c r="A132" s="5" t="s">
+        <v>1900</v>
+      </c>
+      <c r="B132" t="s">
+        <v>1901</v>
+      </c>
+      <c r="C132" t="s">
+        <v>1902</v>
+      </c>
+      <c r="D132">
+        <v>2045413136111</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
+      <c r="A133" s="5" t="s">
+        <v>1903</v>
+      </c>
+      <c r="B133" t="s">
+        <v>1904</v>
+      </c>
+      <c r="C133" t="s">
+        <v>1905</v>
+      </c>
+      <c r="D133">
+        <v>2045411146525</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="A134" s="5" t="s">
+        <v>1906</v>
+      </c>
+      <c r="B134" t="s">
+        <v>1907</v>
+      </c>
+      <c r="C134" t="s">
+        <v>1908</v>
+      </c>
+      <c r="D134">
+        <v>2045413136067</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4">
+      <c r="A135" s="5" t="s">
+        <v>1909</v>
+      </c>
+      <c r="B135" t="s">
+        <v>1910</v>
+      </c>
+      <c r="C135" t="s">
+        <v>1911</v>
+      </c>
+      <c r="D135">
+        <v>2045413136500</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4">
+      <c r="A136" s="5" t="s">
+        <v>1912</v>
+      </c>
+      <c r="B136" t="s">
+        <v>1913</v>
+      </c>
+      <c r="C136" t="s">
+        <v>1914</v>
+      </c>
+      <c r="D136">
+        <v>2045413135879</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4">
+      <c r="A137" s="5" t="s">
+        <v>1915</v>
+      </c>
+      <c r="B137" t="s">
+        <v>1916</v>
+      </c>
+      <c r="C137" t="s">
+        <v>1917</v>
+      </c>
+      <c r="D137">
+        <v>2045413136364</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4">
+      <c r="A138" s="5" t="s">
+        <v>1918</v>
+      </c>
+      <c r="B138" t="s">
+        <v>1919</v>
+      </c>
+      <c r="C138" t="s">
+        <v>1920</v>
+      </c>
+      <c r="D138">
+        <v>2045411146532</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4">
+      <c r="A139" s="5" t="s">
+        <v>1921</v>
+      </c>
+      <c r="B139" t="s">
+        <v>1922</v>
+      </c>
+      <c r="C139" t="s">
+        <v>1923</v>
+      </c>
+      <c r="D139">
+        <v>2045411146549</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4">
+      <c r="A140" s="5" t="s">
+        <v>1924</v>
+      </c>
+      <c r="B140" t="s">
+        <v>1925</v>
+      </c>
+      <c r="C140" t="s">
+        <v>1926</v>
+      </c>
+      <c r="D140">
+        <v>2045411146556</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4">
+      <c r="A141" s="5" t="s">
+        <v>1927</v>
+      </c>
+      <c r="B141" t="s">
+        <v>1928</v>
+      </c>
+      <c r="C141" t="s">
+        <v>1929</v>
+      </c>
+      <c r="D141">
+        <v>2045411146501</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
+      <c r="A142" s="5" t="s">
+        <v>1930</v>
+      </c>
+      <c r="B142" t="s">
+        <v>1931</v>
+      </c>
+      <c r="C142" t="s">
+        <v>1932</v>
+      </c>
+      <c r="D142">
+        <v>2045413136166</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4">
+      <c r="A143" s="5" t="s">
+        <v>1933</v>
+      </c>
+      <c r="B143" t="s">
+        <v>1934</v>
+      </c>
+      <c r="C143" t="s">
+        <v>1935</v>
+      </c>
+      <c r="D143">
+        <v>2045413136470</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4">
+      <c r="A144" s="5" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B144" t="s">
+        <v>1937</v>
+      </c>
+      <c r="C144" t="s">
+        <v>1938</v>
+      </c>
+      <c r="D144">
+        <v>2045413136487</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4">
+      <c r="A145" s="5" t="s">
+        <v>1939</v>
+      </c>
+      <c r="B145" t="s">
+        <v>1940</v>
+      </c>
+      <c r="C145" t="s">
+        <v>1941</v>
+      </c>
+      <c r="D145">
+        <v>2045413136418</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4">
+      <c r="A146" s="5" t="s">
+        <v>1942</v>
+      </c>
+      <c r="B146" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C146" t="s">
+        <v>1944</v>
+      </c>
+      <c r="D146">
+        <v>2045413136050</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4">
+      <c r="A147" s="5" t="s">
+        <v>1945</v>
+      </c>
+      <c r="B147" t="s">
+        <v>1946</v>
+      </c>
+      <c r="C147" t="s">
+        <v>1947</v>
+      </c>
+      <c r="D147">
+        <v>2045413136142</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4">
+      <c r="A148" s="5" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B148" t="s">
+        <v>1949</v>
+      </c>
+      <c r="C148" t="s">
+        <v>1950</v>
+      </c>
+      <c r="D148">
+        <v>2045411146624</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4">
+      <c r="A149" s="5" t="s">
+        <v>1951</v>
+      </c>
+      <c r="B149" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C149" t="s">
+        <v>1953</v>
+      </c>
+      <c r="D149">
+        <v>2045411146587</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4">
+      <c r="A150" s="5" t="s">
+        <v>1954</v>
+      </c>
+      <c r="B150" t="s">
+        <v>1955</v>
+      </c>
+      <c r="C150" t="s">
+        <v>1956</v>
+      </c>
+      <c r="D150">
+        <v>2045413136456</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4">
+      <c r="A151" s="5" t="s">
+        <v>1957</v>
+      </c>
+      <c r="B151" t="s">
+        <v>1958</v>
+      </c>
+      <c r="C151" t="s">
+        <v>1959</v>
+      </c>
+      <c r="D151">
+        <v>2045413136302</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4">
+      <c r="A152" s="5" t="s">
+        <v>1960</v>
+      </c>
+      <c r="B152" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C152" t="s">
+        <v>1962</v>
+      </c>
+      <c r="D152">
+        <v>2045413136425</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4">
+      <c r="A153" s="5" t="s">
+        <v>1963</v>
+      </c>
+      <c r="B153" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C153" t="s">
+        <v>1965</v>
+      </c>
+      <c r="D153">
+        <v>2045413135909</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/compare.xlsx
+++ b/data/compare.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="GT_Byaz_220" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="GT_Poplin_220" sheetId="3" r:id="rId6"/>
     <sheet name="TD" sheetId="4" r:id="rId7"/>
     <sheet name="AD" sheetId="8" r:id="rId8"/>
+    <sheet name="TDL_Byaz_220_solid" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="162913" refMode="R1C1"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2372" uniqueCount="1966">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2434" uniqueCount="2028">
   <si>
     <t>TG1VichyLightBlue220/33</t>
   </si>
@@ -5929,6 +5930,192 @@
   </si>
   <si>
     <t>Я028073</t>
+  </si>
+  <si>
+    <t>TD-BY8-220120-Anis</t>
+  </si>
+  <si>
+    <t>ТТ-00241637</t>
+  </si>
+  <si>
+    <t>TD-BY8-220120-Arona</t>
+  </si>
+  <si>
+    <t>ТТ-00273964</t>
+  </si>
+  <si>
+    <t>TD-BY8-220120-Beige</t>
+  </si>
+  <si>
+    <t>TD-BY8-220120-Bordo</t>
+  </si>
+  <si>
+    <t>ТТ-00256872</t>
+  </si>
+  <si>
+    <t>TD-BY8-220120-Vinograd</t>
+  </si>
+  <si>
+    <t>ТТ-00337331</t>
+  </si>
+  <si>
+    <t>TD-BY8-220120-Vintage</t>
+  </si>
+  <si>
+    <t>ТТ-00254441</t>
+  </si>
+  <si>
+    <t>TD-BY8-220120-LightBlue</t>
+  </si>
+  <si>
+    <t>TD-BY8-220120-GorkChoco</t>
+  </si>
+  <si>
+    <t>ТТ-00212143</t>
+  </si>
+  <si>
+    <t>TD-BY8-220120-Grafit</t>
+  </si>
+  <si>
+    <t>ТТ-00247976</t>
+  </si>
+  <si>
+    <t>TD-BY8-220120-DenimNEO</t>
+  </si>
+  <si>
+    <t>ТТ-00331831</t>
+  </si>
+  <si>
+    <t>TD-BY8-220120-DimchatayaRoza</t>
+  </si>
+  <si>
+    <t>TD-BY8-220120-Demson</t>
+  </si>
+  <si>
+    <t>ТТ-00331832</t>
+  </si>
+  <si>
+    <t>TD-BY8-220120-Capuccino</t>
+  </si>
+  <si>
+    <t>ТТ-00309193</t>
+  </si>
+  <si>
+    <t>TD-BY8-220120-CoffeeMilk</t>
+  </si>
+  <si>
+    <t>TD-BY8-220120-Cream</t>
+  </si>
+  <si>
+    <t>ТТ-00236352</t>
+  </si>
+  <si>
+    <t>TD-BY8-220120-Crocus</t>
+  </si>
+  <si>
+    <t>ТТ-00336612</t>
+  </si>
+  <si>
+    <t>TD-BY8-220120-Lavanda</t>
+  </si>
+  <si>
+    <t>TD-BY8-220140-Malina140</t>
+  </si>
+  <si>
+    <t>ТТ-00335066</t>
+  </si>
+  <si>
+    <t>TD-BY8-220140-Mocco140</t>
+  </si>
+  <si>
+    <t>ТТ-00304047</t>
+  </si>
+  <si>
+    <t>TD-BY8-220120-Mouse</t>
+  </si>
+  <si>
+    <t>ТТ-00328442</t>
+  </si>
+  <si>
+    <t>TD-BY8-220120-NebesnoGoluboi</t>
+  </si>
+  <si>
+    <t>TD-BY8-220120-Nebesniy</t>
+  </si>
+  <si>
+    <t>ТТ-00235918</t>
+  </si>
+  <si>
+    <t>TD-BY8-220120-Nefrit</t>
+  </si>
+  <si>
+    <t>ТТ-00242745</t>
+  </si>
+  <si>
+    <t>TD-BY8-220120-Oliva</t>
+  </si>
+  <si>
+    <t>ТТ-00234226</t>
+  </si>
+  <si>
+    <t>TD-BY8-220120-PowderPink</t>
+  </si>
+  <si>
+    <t>TD-BY8-220120-GreySmoke</t>
+  </si>
+  <si>
+    <t>ТТ-00271958</t>
+  </si>
+  <si>
+    <t>TD-BY8-220120-Blue</t>
+  </si>
+  <si>
+    <t>ТТ-00277992</t>
+  </si>
+  <si>
+    <t>TD-BY8-220120-Sliva</t>
+  </si>
+  <si>
+    <t>ТТ-00236355</t>
+  </si>
+  <si>
+    <t>TD-BY8-220120-Slivochniy</t>
+  </si>
+  <si>
+    <t>TD-BY8-220120-Sunny</t>
+  </si>
+  <si>
+    <t>ТТ-00289061</t>
+  </si>
+  <si>
+    <t>TD-BY8-220120-AquamarineDark</t>
+  </si>
+  <si>
+    <t>TD-BY8-220120-VasilekDark</t>
+  </si>
+  <si>
+    <t>ТТ-00248748</t>
+  </si>
+  <si>
+    <t>TD-BY8-220120-Violet</t>
+  </si>
+  <si>
+    <t>TD-BY8-220120-FrancGrey</t>
+  </si>
+  <si>
+    <t>ТТ-00234230</t>
+  </si>
+  <si>
+    <t>TD-BY8-220140-Black140</t>
+  </si>
+  <si>
+    <t>ТТ-00248750</t>
+  </si>
+  <si>
+    <t>TD-BY8-220120-sherl</t>
+  </si>
+  <si>
+    <t>ТТ-00328443</t>
   </si>
 </sst>
 </file>
@@ -16718,4 +16905,306 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B36"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="33.25" customWidth="1"/>
+    <col min="2" max="2" width="23.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="5" t="s">
+        <v>1966</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1967</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="5" t="s">
+        <v>1968</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>1969</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="5" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B3" s="6">
+        <v>148154</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="5" t="s">
+        <v>1971</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="5" t="s">
+        <v>1973</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="5" t="s">
+        <v>1975</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>1976</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="5" t="s">
+        <v>1977</v>
+      </c>
+      <c r="B7" s="6">
+        <v>147483</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="5" t="s">
+        <v>1978</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="5" t="s">
+        <v>1980</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="5" t="s">
+        <v>1982</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>1983</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="5" t="s">
+        <v>1984</v>
+      </c>
+      <c r="B11" s="6">
+        <v>146655</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="5" t="s">
+        <v>1985</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>1986</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="5" t="s">
+        <v>1987</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>1988</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="5" t="s">
+        <v>1989</v>
+      </c>
+      <c r="B14" s="6">
+        <v>150587</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="5" t="s">
+        <v>1990</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="5" t="s">
+        <v>1992</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="5" t="s">
+        <v>1994</v>
+      </c>
+      <c r="B17" s="6">
+        <v>186976</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="5" t="s">
+        <v>1995</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="5" t="s">
+        <v>1997</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="5" t="s">
+        <v>1999</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="5" t="s">
+        <v>2001</v>
+      </c>
+      <c r="B21" s="6">
+        <v>171073</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="5" t="s">
+        <v>2002</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="5" t="s">
+        <v>2004</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="5" t="s">
+        <v>2006</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="5" t="s">
+        <v>2008</v>
+      </c>
+      <c r="B25" s="6">
+        <v>184393</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="5" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="5" t="s">
+        <v>2011</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="5" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="5" t="s">
+        <v>2015</v>
+      </c>
+      <c r="B29" s="6">
+        <v>203531</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="5" t="s">
+        <v>2016</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="5" t="s">
+        <v>2018</v>
+      </c>
+      <c r="B31" s="6">
+        <v>215647</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="5" t="s">
+        <v>2019</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="5" t="s">
+        <v>2021</v>
+      </c>
+      <c r="B33" s="6">
+        <v>148155</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="5" t="s">
+        <v>2022</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="5" t="s">
+        <v>2024</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="5" t="s">
+        <v>2026</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>2027</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>